--- a/app/analytical-backend/data/07_model_output/ar.xlsx
+++ b/app/analytical-backend/data/07_model_output/ar.xlsx
@@ -468,7 +468,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.9946202984165897</v>
+        <v>0.9946202983824494</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -476,7 +476,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002176552418256159</v>
+        <v>0.00217655242475648</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>152.2746023045191</v>
+        <v>152.2746027876978</v>
       </c>
     </row>
   </sheetData>
@@ -2988,7 +2988,7 @@
         <v>43374</v>
       </c>
       <c r="B227">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="C227">
         <v>13727.1</v>
@@ -2999,7 +2999,7 @@
         <v>43405</v>
       </c>
       <c r="B228">
-        <v>13762.14655938816</v>
+        <v>13762.14655939053</v>
       </c>
       <c r="C228">
         <v>13800.3</v>
@@ -3010,7 +3010,7 @@
         <v>43435</v>
       </c>
       <c r="B229">
-        <v>13820.54392215984</v>
+        <v>13820.54392215916</v>
       </c>
       <c r="C229">
         <v>13682.3</v>
@@ -3021,7 +3021,7 @@
         <v>43466</v>
       </c>
       <c r="B230">
-        <v>13723.8440850211</v>
+        <v>13723.84408502984</v>
       </c>
       <c r="C230">
         <v>13716.5</v>
@@ -3032,7 +3032,7 @@
         <v>43497</v>
       </c>
       <c r="B231">
-        <v>13764.31487604686</v>
+        <v>13764.31487605275</v>
       </c>
       <c r="C231">
         <v>13723.1</v>
@@ -3043,7 +3043,7 @@
         <v>43525</v>
       </c>
       <c r="B232">
-        <v>13735.02464504945</v>
+        <v>13735.02464505133</v>
       </c>
       <c r="C232">
         <v>13818.2</v>
@@ -3054,7 +3054,7 @@
         <v>43556</v>
       </c>
       <c r="B233">
-        <v>13848.81486970803</v>
+        <v>13848.81486970863</v>
       </c>
       <c r="C233">
         <v>13813.1</v>
@@ -3076,7 +3076,7 @@
         <v>43617</v>
       </c>
       <c r="B235">
-        <v>13912.53444759663</v>
+        <v>13912.5344475934</v>
       </c>
       <c r="C235">
         <v>13909.09999999999</v>
@@ -3087,7 +3087,7 @@
         <v>43647</v>
       </c>
       <c r="B236">
-        <v>13935.17934710532</v>
+        <v>13935.17934710672</v>
       </c>
       <c r="C236">
         <v>13968.4</v>
@@ -3098,7 +3098,7 @@
         <v>43678</v>
       </c>
       <c r="B237">
-        <v>14003.01220215172</v>
+        <v>14003.01220207311</v>
       </c>
       <c r="C237">
         <v>14013.2</v>
@@ -3109,7 +3109,7 @@
         <v>43709</v>
       </c>
       <c r="B238">
-        <v>14046.40905810868</v>
+        <v>14046.40905817672</v>
       </c>
       <c r="C238">
         <v>14029.7</v>
@@ -3120,7 +3120,7 @@
         <v>43739</v>
       </c>
       <c r="B239">
-        <v>14068.36017746287</v>
+        <v>14068.36017744439</v>
       </c>
       <c r="C239">
         <v>14029.09999999999</v>
@@ -3131,7 +3131,7 @@
         <v>43770</v>
       </c>
       <c r="B240">
-        <v>14067.62969454793</v>
+        <v>14067.62969457345</v>
       </c>
       <c r="C240">
         <v>14115.39999999999</v>
@@ -3142,7 +3142,7 @@
         <v>43800</v>
       </c>
       <c r="B241">
-        <v>14144.31838326521</v>
+        <v>14144.3183830814</v>
       </c>
       <c r="C241">
         <v>14137.09999999999</v>
@@ -3153,7 +3153,7 @@
         <v>43831</v>
       </c>
       <c r="B242">
-        <v>14163.17337706021</v>
+        <v>14163.1733770597</v>
       </c>
       <c r="C242">
         <v>14184.79999999999</v>
@@ -3164,7 +3164,7 @@
         <v>43862</v>
       </c>
       <c r="B243">
-        <v>14227.57980055274</v>
+        <v>14227.57980265306</v>
       </c>
       <c r="C243">
         <v>14167.79999999999</v>
@@ -3175,7 +3175,7 @@
         <v>43891</v>
       </c>
       <c r="B244">
-        <v>14202.34670413345</v>
+        <v>14202.3467041327</v>
       </c>
       <c r="C244">
         <v>13234.29999999999</v>
@@ -3186,7 +3186,7 @@
         <v>43922</v>
       </c>
       <c r="B245">
-        <v>13298.35997385564</v>
+        <v>13298.36003798657</v>
       </c>
       <c r="C245">
         <v>11783.29999999999</v>
@@ -3197,7 +3197,7 @@
         <v>43952</v>
       </c>
       <c r="B246">
-        <v>11140.77789757389</v>
+        <v>11140.77794425926</v>
       </c>
       <c r="C246">
         <v>12757.99999999999</v>
@@ -3219,7 +3219,7 @@
         <v>44013</v>
       </c>
       <c r="B248">
-        <v>13170.83648895239</v>
+        <v>13170.83648895002</v>
       </c>
       <c r="C248">
         <v>13667.29999999999</v>
@@ -3230,7 +3230,7 @@
         <v>44044</v>
       </c>
       <c r="B249">
-        <v>13600.60622413137</v>
+        <v>13600.60622417108</v>
       </c>
       <c r="C249">
         <v>13761.09999999999</v>
@@ -3241,7 +3241,7 @@
         <v>44075</v>
       </c>
       <c r="B250">
-        <v>13675.15139630761</v>
+        <v>13675.15139658909</v>
       </c>
       <c r="C250">
         <v>13953.39999999999</v>
@@ -3252,7 +3252,7 @@
         <v>44105</v>
       </c>
       <c r="B251">
-        <v>13937.66236999403</v>
+        <v>13937.66236998339</v>
       </c>
       <c r="C251">
         <v>13988.6</v>
@@ -3263,7 +3263,7 @@
         <v>44136</v>
       </c>
       <c r="B252">
-        <v>13886.75742989805</v>
+        <v>13886.75742953947</v>
       </c>
       <c r="C252">
         <v>13953.9</v>
@@ -3274,7 +3274,7 @@
         <v>44166</v>
       </c>
       <c r="B253">
-        <v>13933.50902581842</v>
+        <v>13933.50902580089</v>
       </c>
       <c r="C253">
         <v>14006.3</v>
@@ -3285,7 +3285,7 @@
         <v>44197</v>
       </c>
       <c r="B254">
-        <v>14012.54768447861</v>
+        <v>14012.54768443149</v>
       </c>
       <c r="C254">
         <v>14180.7</v>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="B255">
-        <v>14194.77140487092</v>
+        <v>14194.77140486521</v>
       </c>
       <c r="C255">
         <v>14037.8</v>
@@ -3307,7 +3307,7 @@
         <v>44256</v>
       </c>
       <c r="B256">
-        <v>13989.61353130077</v>
+        <v>13989.61353131358</v>
       </c>
       <c r="C256">
         <v>14629.3</v>
@@ -3318,7 +3318,7 @@
         <v>44287</v>
       </c>
       <c r="B257">
-        <v>14742.00059507452</v>
+        <v>14742.00059505072</v>
       </c>
       <c r="C257">
         <v>14730.7</v>
@@ -3329,7 +3329,7 @@
         <v>44317</v>
       </c>
       <c r="B258">
-        <v>14572.8232581742</v>
+        <v>14572.8232582088</v>
       </c>
       <c r="C258">
         <v>14689.59999999999</v>
@@ -3340,7 +3340,7 @@
         <v>44348</v>
       </c>
       <c r="B259">
-        <v>14674.8618822172</v>
+        <v>14674.86188227729</v>
       </c>
       <c r="C259">
         <v>14816.39999999999</v>
@@ -3351,7 +3351,7 @@
         <v>44378</v>
       </c>
       <c r="B260">
-        <v>14814.05662571575</v>
+        <v>14814.05662577054</v>
       </c>
       <c r="C260">
         <v>14784</v>
@@ -3362,7 +3362,7 @@
         <v>44409</v>
       </c>
       <c r="B261">
-        <v>14762.32679598055</v>
+        <v>14762.32679604099</v>
       </c>
       <c r="C261">
         <v>14863</v>
@@ -3373,7 +3373,7 @@
         <v>44440</v>
       </c>
       <c r="B262">
-        <v>14921.66825324265</v>
+        <v>14921.66825324755</v>
       </c>
       <c r="C262">
         <v>14899.4</v>
@@ -3384,7 +3384,7 @@
         <v>44470</v>
       </c>
       <c r="B263">
-        <v>14924.32005935037</v>
+        <v>14924.32005934976</v>
       </c>
       <c r="C263">
         <v>14997.3</v>
@@ -3395,7 +3395,7 @@
         <v>44501</v>
       </c>
       <c r="B264">
-        <v>15039.66444965629</v>
+        <v>15039.66444965966</v>
       </c>
       <c r="C264">
         <v>15019.2</v>
@@ -3406,7 +3406,7 @@
         <v>44531</v>
       </c>
       <c r="B265">
-        <v>15038.3227329279</v>
+        <v>15038.32273293419</v>
       </c>
       <c r="C265">
         <v>14970.4</v>
@@ -3417,7 +3417,7 @@
         <v>44562</v>
       </c>
       <c r="B266">
-        <v>15003.5253504174</v>
+        <v>15003.52535041061</v>
       </c>
       <c r="C266">
         <v>14971.1</v>
@@ -3428,7 +3428,7 @@
         <v>44593</v>
       </c>
       <c r="B267">
-        <v>15027.26756896857</v>
+        <v>15027.26756896379</v>
       </c>
       <c r="C267">
         <v>14980.6</v>
@@ -3439,7 +3439,7 @@
         <v>44621</v>
       </c>
       <c r="B268">
-        <v>15024.15350385069</v>
+        <v>15024.15350384804</v>
       </c>
       <c r="C268">
         <v>15034</v>
@@ -3450,7 +3450,7 @@
         <v>44652</v>
       </c>
       <c r="B269">
-        <v>15079.23873306349</v>
+        <v>15079.23873306312</v>
       </c>
       <c r="C269">
         <v>15081.7</v>
@@ -3461,7 +3461,7 @@
         <v>44682</v>
       </c>
       <c r="B270">
-        <v>15114.75763204146</v>
+        <v>15114.75763203552</v>
       </c>
       <c r="C270">
         <v>15060</v>
@@ -3472,7 +3472,7 @@
         <v>44713</v>
       </c>
       <c r="B271">
-        <v>15088.31022614576</v>
+        <v>15088.31022614903</v>
       </c>
       <c r="C271">
         <v>15065.8</v>
@@ -3483,7 +3483,7 @@
         <v>44743</v>
       </c>
       <c r="B272">
-        <v>15115.02537905343</v>
+        <v>15115.02537905775</v>
       </c>
       <c r="C272">
         <v>15069.1</v>
@@ -3494,7 +3494,7 @@
         <v>44774</v>
       </c>
       <c r="B273">
-        <v>15110.57904251102</v>
+        <v>15110.57904251638</v>
       </c>
       <c r="C273">
         <v>15136.3</v>
@@ -3505,7 +3505,7 @@
         <v>44805</v>
       </c>
       <c r="B274">
-        <v>15184.36200049745</v>
+        <v>15184.36200049382</v>
       </c>
       <c r="C274">
         <v>15176.7</v>
@@ -3516,7 +3516,7 @@
         <v>44835</v>
       </c>
       <c r="B275">
-        <v>15205.27405093052</v>
+        <v>15205.27405092593</v>
       </c>
       <c r="C275">
         <v>15202.7</v>
@@ -3527,7 +3527,7 @@
         <v>44866</v>
       </c>
       <c r="B276">
-        <v>15237.31738989229</v>
+        <v>15237.31738989649</v>
       </c>
       <c r="C276">
         <v>15149.8</v>
@@ -3538,7 +3538,7 @@
         <v>44896</v>
       </c>
       <c r="B277">
-        <v>15180.9493755844</v>
+        <v>15180.94937558075</v>
       </c>
       <c r="C277">
         <v>15161.7</v>
@@ -3549,7 +3549,7 @@
         <v>44927</v>
       </c>
       <c r="B278">
-        <v>15219.52623355066</v>
+        <v>15219.52623354855</v>
       </c>
       <c r="C278">
         <v>15317.6</v>
@@ -3560,7 +3560,7 @@
         <v>44958</v>
       </c>
       <c r="B279">
-        <v>15376.13275649825</v>
+        <v>15376.13275642525</v>
       </c>
       <c r="C279">
         <v>15325.5</v>
@@ -3571,7 +3571,7 @@
         <v>44986</v>
       </c>
       <c r="B280">
-        <v>15335.12124577368</v>
+        <v>15335.12124575278</v>
       </c>
       <c r="C280">
         <v>15295.4</v>
@@ -3582,7 +3582,7 @@
         <v>45017</v>
       </c>
       <c r="B281">
-        <v>15337.2602703197</v>
+        <v>15337.26027031327</v>
       </c>
       <c r="C281">
         <v>15316.9</v>
@@ -3593,7 +3593,7 @@
         <v>45047</v>
       </c>
       <c r="B282">
-        <v>15366.06093841186</v>
+        <v>15366.06093841196</v>
       </c>
       <c r="C282">
         <v>15337.4</v>
@@ -3604,7 +3604,7 @@
         <v>45078</v>
       </c>
       <c r="B283">
-        <v>15381.92479863529</v>
+        <v>15381.92479863971</v>
       </c>
       <c r="C283">
         <v>15376.3</v>
@@ -3615,7 +3615,7 @@
         <v>45108</v>
       </c>
       <c r="B284">
-        <v>15423.92662020425</v>
+        <v>15423.92662020543</v>
       </c>
       <c r="C284">
         <v>15448.3</v>
@@ -3626,7 +3626,7 @@
         <v>45139</v>
       </c>
       <c r="B285">
-        <v>15487.64743561486</v>
+        <v>15487.64743561261</v>
       </c>
       <c r="C285">
         <v>15439.79999999999</v>
@@ -3637,7 +3637,7 @@
         <v>45170</v>
       </c>
       <c r="B286">
-        <v>15466.87152790177</v>
+        <v>15466.87152790476</v>
       </c>
       <c r="C286">
         <v>15495.99999999999</v>
@@ -3659,7 +3659,7 @@
         <v>45231</v>
       </c>
       <c r="B288">
-        <v>15550.43462008552</v>
+        <v>15550.43462007772</v>
       </c>
       <c r="C288">
         <v>15584.29999999999</v>
@@ -3670,7 +3670,7 @@
         <v>45261</v>
       </c>
       <c r="B289">
-        <v>15627.38005936063</v>
+        <v>15627.3800593587</v>
       </c>
       <c r="C289">
         <v>15655.79999999999</v>
@@ -3703,7 +3703,7 @@
         <v>45352</v>
       </c>
       <c r="B292">
-        <v>15700.08794333444</v>
+        <v>15700.08794332679</v>
       </c>
       <c r="C292">
         <v>15689.59999999999</v>
@@ -3714,7 +3714,7 @@
         <v>45383</v>
       </c>
       <c r="B293">
-        <v>15728.08343082395</v>
+        <v>15728.08343082644</v>
       </c>
       <c r="C293">
         <v>15685.59999999999</v>
@@ -3736,7 +3736,7 @@
         <v>45444</v>
       </c>
       <c r="B295">
-        <v>15821.83531716459</v>
+        <v>15821.83531715635</v>
       </c>
       <c r="C295">
         <v>15810.7</v>
@@ -3747,7 +3747,7 @@
         <v>45474</v>
       </c>
       <c r="B296">
-        <v>15836.07895612765</v>
+        <v>15836.0789561283</v>
       </c>
       <c r="C296">
         <v>15870.29999999999</v>
@@ -3758,7 +3758,7 @@
         <v>45505</v>
       </c>
       <c r="B297">
-        <v>15911.45000807181</v>
+        <v>15911.45000806028</v>
       </c>
       <c r="C297">
         <v>16089.69999999999</v>
@@ -3816,19 +3816,19 @@
         <v>43374</v>
       </c>
       <c r="B3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="C3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="D3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="E3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="F3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3836,19 +3836,19 @@
         <v>43405</v>
       </c>
       <c r="B4">
-        <v>13720.13829566091</v>
+        <v>13720.13829566305</v>
       </c>
       <c r="C4">
-        <v>13804.15482311541</v>
+        <v>13804.15482311802</v>
       </c>
       <c r="D4">
-        <v>13636.1217682064</v>
+        <v>13636.12176820807</v>
       </c>
       <c r="E4">
-        <v>13888.17135056992</v>
+        <v>13888.171350573</v>
       </c>
       <c r="F4">
-        <v>13762.14655938816</v>
+        <v>13762.14655939053</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3856,19 +3856,19 @@
         <v>43435</v>
       </c>
       <c r="B5">
-        <v>13773.09436545825</v>
+        <v>13773.09436545861</v>
       </c>
       <c r="C5">
-        <v>13867.99347886143</v>
+        <v>13867.99347885971</v>
       </c>
       <c r="D5">
-        <v>13678.19525205506</v>
+        <v>13678.19525205751</v>
       </c>
       <c r="E5">
-        <v>13962.89259226462</v>
+        <v>13962.89259226081</v>
       </c>
       <c r="F5">
-        <v>13820.54392215984</v>
+        <v>13820.54392215916</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3876,19 +3876,19 @@
         <v>43466</v>
       </c>
       <c r="B6">
-        <v>13647.10123165385</v>
+        <v>13647.1012316636</v>
       </c>
       <c r="C6">
-        <v>13800.58693838835</v>
+        <v>13800.58693839608</v>
       </c>
       <c r="D6">
-        <v>13493.61552491934</v>
+        <v>13493.61552493111</v>
       </c>
       <c r="E6">
-        <v>13954.07264512285</v>
+        <v>13954.07264512857</v>
       </c>
       <c r="F6">
-        <v>13723.8440850211</v>
+        <v>13723.84408502984</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3896,19 +3896,19 @@
         <v>43497</v>
       </c>
       <c r="B7">
-        <v>13696.33813430579</v>
+        <v>13696.33813431328</v>
       </c>
       <c r="C7">
-        <v>13832.29161778794</v>
+        <v>13832.29161779222</v>
       </c>
       <c r="D7">
-        <v>13560.38465082363</v>
+        <v>13560.38465083433</v>
       </c>
       <c r="E7">
-        <v>13968.2451012701</v>
+        <v>13968.24510127117</v>
       </c>
       <c r="F7">
-        <v>13764.31487604686</v>
+        <v>13764.31487605275</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3916,19 +3916,19 @@
         <v>43525</v>
       </c>
       <c r="B8">
-        <v>13674.06508443986</v>
+        <v>13674.06508444306</v>
       </c>
       <c r="C8">
-        <v>13795.98420565905</v>
+        <v>13795.98420565959</v>
       </c>
       <c r="D8">
-        <v>13552.14596322067</v>
+        <v>13552.14596322653</v>
       </c>
       <c r="E8">
-        <v>13917.90332687824</v>
+        <v>13917.90332687612</v>
       </c>
       <c r="F8">
-        <v>13735.02464504945</v>
+        <v>13735.02464505133</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3936,19 +3936,19 @@
         <v>43556</v>
       </c>
       <c r="B9">
-        <v>13777.41152162746</v>
+        <v>13777.41152162883</v>
       </c>
       <c r="C9">
-        <v>13920.21821778861</v>
+        <v>13920.21821778843</v>
       </c>
       <c r="D9">
-        <v>13634.60482546631</v>
+        <v>13634.60482546922</v>
       </c>
       <c r="E9">
-        <v>14063.02491394976</v>
+        <v>14063.02491394804</v>
       </c>
       <c r="F9">
-        <v>13848.81486970803</v>
+        <v>13848.81486970863</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3956,16 +3956,16 @@
         <v>43586</v>
       </c>
       <c r="B10">
-        <v>13770.02614910731</v>
+        <v>13770.02614910809</v>
       </c>
       <c r="C10">
-        <v>13902.87858218283</v>
+        <v>13902.87858218205</v>
       </c>
       <c r="D10">
-        <v>13637.17371603179</v>
+        <v>13637.17371603413</v>
       </c>
       <c r="E10">
-        <v>14035.73101525835</v>
+        <v>14035.73101525601</v>
       </c>
       <c r="F10">
         <v>13836.45236564507</v>
@@ -3976,19 +3976,19 @@
         <v>43617</v>
       </c>
       <c r="B11">
-        <v>13848.0714537819</v>
+        <v>13848.07145377918</v>
       </c>
       <c r="C11">
-        <v>13976.99744141136</v>
+        <v>13976.99744140761</v>
       </c>
       <c r="D11">
-        <v>13719.14546615244</v>
+        <v>13719.14546615075</v>
       </c>
       <c r="E11">
-        <v>14105.92342904081</v>
+        <v>14105.92342903604</v>
       </c>
       <c r="F11">
-        <v>13912.53444759663</v>
+        <v>13912.5344475934</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3996,19 +3996,19 @@
         <v>43647</v>
       </c>
       <c r="B12">
-        <v>13874.12867182962</v>
+        <v>13874.12867183141</v>
       </c>
       <c r="C12">
-        <v>13996.23002238103</v>
+        <v>13996.23002238203</v>
       </c>
       <c r="D12">
-        <v>13752.02732127821</v>
+        <v>13752.0273212808</v>
       </c>
       <c r="E12">
-        <v>14118.33137293243</v>
+        <v>14118.33137293264</v>
       </c>
       <c r="F12">
-        <v>13935.17934710532</v>
+        <v>13935.17934710672</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4016,19 +4016,19 @@
         <v>43678</v>
       </c>
       <c r="B13">
-        <v>13943.21146214525</v>
+        <v>13943.21146206699</v>
       </c>
       <c r="C13">
-        <v>14062.81294215819</v>
+        <v>14062.81294207923</v>
       </c>
       <c r="D13">
-        <v>13823.6099821323</v>
+        <v>13823.60998205476</v>
       </c>
       <c r="E13">
-        <v>14182.41442217114</v>
+        <v>14182.41442209146</v>
       </c>
       <c r="F13">
-        <v>14003.01220215172</v>
+        <v>14003.01220207311</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4036,19 +4036,19 @@
         <v>43709</v>
       </c>
       <c r="B14">
-        <v>13988.95228625303</v>
+        <v>13988.95228631921</v>
       </c>
       <c r="C14">
-        <v>14103.86582996434</v>
+        <v>14103.86583003423</v>
       </c>
       <c r="D14">
-        <v>13874.03874254172</v>
+        <v>13874.0387426042</v>
       </c>
       <c r="E14">
-        <v>14218.77937367565</v>
+        <v>14218.77937374924</v>
       </c>
       <c r="F14">
-        <v>14046.40905810868</v>
+        <v>14046.40905817672</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4056,19 +4056,19 @@
         <v>43739</v>
       </c>
       <c r="B15">
-        <v>14013.21862204888</v>
+        <v>14013.21862202763</v>
       </c>
       <c r="C15">
-        <v>14123.50173287685</v>
+        <v>14123.50173286114</v>
       </c>
       <c r="D15">
-        <v>13902.9355112209</v>
+        <v>13902.93551119412</v>
       </c>
       <c r="E15">
-        <v>14233.78484370483</v>
+        <v>14233.78484369466</v>
       </c>
       <c r="F15">
-        <v>14068.36017746287</v>
+        <v>14068.36017744439</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4076,19 +4076,19 @@
         <v>43770</v>
       </c>
       <c r="B16">
-        <v>14013.98830969148</v>
+        <v>14013.98830971517</v>
       </c>
       <c r="C16">
-        <v>14121.27107940438</v>
+        <v>14121.27107943173</v>
       </c>
       <c r="D16">
-        <v>13906.70553997858</v>
+        <v>13906.70553999861</v>
       </c>
       <c r="E16">
-        <v>14228.55384911728</v>
+        <v>14228.55384914829</v>
       </c>
       <c r="F16">
-        <v>14067.62969454793</v>
+        <v>14067.62969457345</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4096,19 +4096,19 @@
         <v>43800</v>
       </c>
       <c r="B17">
-        <v>14090.18848166501</v>
+        <v>14090.18848148139</v>
       </c>
       <c r="C17">
-        <v>14198.44828486541</v>
+        <v>14198.4482846814</v>
       </c>
       <c r="D17">
-        <v>13981.9286784646</v>
+        <v>13981.92867828138</v>
       </c>
       <c r="E17">
-        <v>14306.70808806581</v>
+        <v>14306.70808788141</v>
       </c>
       <c r="F17">
-        <v>14144.31838326521</v>
+        <v>14144.3183830814</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4116,19 +4116,19 @@
         <v>43831</v>
       </c>
       <c r="B18">
-        <v>14110.79788747252</v>
+        <v>14110.79788747244</v>
       </c>
       <c r="C18">
-        <v>14215.54886664789</v>
+        <v>14215.54886664696</v>
       </c>
       <c r="D18">
-        <v>14006.04690829716</v>
+        <v>14006.04690829792</v>
       </c>
       <c r="E18">
-        <v>14320.29984582325</v>
+        <v>14320.29984582148</v>
       </c>
       <c r="F18">
-        <v>14163.17337706021</v>
+        <v>14163.1733770597</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4136,19 +4136,19 @@
         <v>43862</v>
       </c>
       <c r="B19">
-        <v>14176.24590498622</v>
+        <v>14176.24590708726</v>
       </c>
       <c r="C19">
-        <v>14278.91369611927</v>
+        <v>14278.91369821885</v>
       </c>
       <c r="D19">
-        <v>14073.57811385317</v>
+        <v>14073.57811595567</v>
       </c>
       <c r="E19">
-        <v>14381.58148725233</v>
+        <v>14381.58148935045</v>
       </c>
       <c r="F19">
-        <v>14227.57980055274</v>
+        <v>14227.57980265306</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4156,19 +4156,19 @@
         <v>43891</v>
       </c>
       <c r="B20">
-        <v>14150.93878897787</v>
+        <v>14150.93878885233</v>
       </c>
       <c r="C20">
-        <v>14253.75461928903</v>
+        <v>14253.75461941308</v>
       </c>
       <c r="D20">
-        <v>14048.1229586667</v>
+        <v>14048.12295829159</v>
       </c>
       <c r="E20">
-        <v>14356.57044960021</v>
+        <v>14356.57044997382</v>
       </c>
       <c r="F20">
-        <v>14202.34670413345</v>
+        <v>14202.3467041327</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4176,19 +4176,19 @@
         <v>43922</v>
       </c>
       <c r="B21">
-        <v>13087.33016305122</v>
+        <v>13087.33022717962</v>
       </c>
       <c r="C21">
-        <v>13509.38978466006</v>
+        <v>13509.38984879352</v>
       </c>
       <c r="D21">
-        <v>12665.27054144238</v>
+        <v>12665.27060556572</v>
       </c>
       <c r="E21">
-        <v>13931.4494062689</v>
+        <v>13931.44947040742</v>
       </c>
       <c r="F21">
-        <v>13298.35997385564</v>
+        <v>13298.36003798657</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4196,19 +4196,19 @@
         <v>43952</v>
       </c>
       <c r="B22">
-        <v>10797.24768653842</v>
+        <v>10797.24772243033</v>
       </c>
       <c r="C22">
-        <v>11484.30810860936</v>
+        <v>11484.30816608818</v>
       </c>
       <c r="D22">
-        <v>10110.18726446749</v>
+        <v>10110.18727877248</v>
       </c>
       <c r="E22">
-        <v>12171.36853068029</v>
+        <v>12171.36860974603</v>
       </c>
       <c r="F22">
-        <v>11140.77789757389</v>
+        <v>11140.77794425926</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4216,16 +4216,16 @@
         <v>43983</v>
       </c>
       <c r="B23">
-        <v>12794.01683542925</v>
+        <v>12794.01683560756</v>
       </c>
       <c r="C23">
-        <v>13886.95868693793</v>
+        <v>13886.95868675962</v>
       </c>
       <c r="D23">
-        <v>11701.07498392056</v>
+        <v>11701.0749844555</v>
       </c>
       <c r="E23">
-        <v>14979.90053844661</v>
+        <v>14979.90053791168</v>
       </c>
       <c r="F23">
         <v>13340.48776118359</v>
@@ -4236,19 +4236,19 @@
         <v>44013</v>
       </c>
       <c r="B24">
-        <v>12606.86969948374</v>
+        <v>12606.86969958762</v>
       </c>
       <c r="C24">
-        <v>13734.80327842104</v>
+        <v>13734.80327831241</v>
       </c>
       <c r="D24">
-        <v>11478.93612054644</v>
+        <v>11478.93612086283</v>
       </c>
       <c r="E24">
-        <v>14862.73685735835</v>
+        <v>14862.73685703721</v>
       </c>
       <c r="F24">
-        <v>13170.83648895239</v>
+        <v>13170.83648895002</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4256,19 +4256,19 @@
         <v>44044</v>
       </c>
       <c r="B25">
-        <v>13030.41443258497</v>
+        <v>13030.41443250244</v>
       </c>
       <c r="C25">
-        <v>14170.79801567777</v>
+        <v>14170.79801583971</v>
       </c>
       <c r="D25">
-        <v>11890.03084949216</v>
+        <v>11890.03084916516</v>
       </c>
       <c r="E25">
-        <v>15311.18159877057</v>
+        <v>15311.18159917699</v>
       </c>
       <c r="F25">
-        <v>13600.60622413137</v>
+        <v>13600.60622417108</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4276,19 +4276,19 @@
         <v>44075</v>
       </c>
       <c r="B26">
-        <v>13112.63410669227</v>
+        <v>13112.63410678798</v>
       </c>
       <c r="C26">
-        <v>14237.66868592295</v>
+        <v>14237.6686863902</v>
       </c>
       <c r="D26">
-        <v>11987.59952746159</v>
+        <v>11987.59952718576</v>
       </c>
       <c r="E26">
-        <v>15362.70326515362</v>
+        <v>15362.70326599242</v>
       </c>
       <c r="F26">
-        <v>13675.15139630761</v>
+        <v>13675.15139658909</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4296,19 +4296,19 @@
         <v>44105</v>
       </c>
       <c r="B27">
-        <v>13376.48504803431</v>
+        <v>13376.48504774195</v>
       </c>
       <c r="C27">
-        <v>14498.83969195375</v>
+        <v>14498.83969222484</v>
       </c>
       <c r="D27">
-        <v>12254.13040411486</v>
+        <v>12254.13040325906</v>
       </c>
       <c r="E27">
-        <v>15621.1943358732</v>
+        <v>15621.19433670773</v>
       </c>
       <c r="F27">
-        <v>13937.66236999403</v>
+        <v>13937.66236998339</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4316,19 +4316,19 @@
         <v>44136</v>
       </c>
       <c r="B28">
-        <v>13335.48060047098</v>
+        <v>13335.48059982235</v>
       </c>
       <c r="C28">
-        <v>14438.03425932512</v>
+        <v>14438.03425925659</v>
       </c>
       <c r="D28">
-        <v>12232.92694161684</v>
+        <v>12232.92694038811</v>
       </c>
       <c r="E28">
-        <v>15540.58791817926</v>
+        <v>15540.58791869083</v>
       </c>
       <c r="F28">
-        <v>13886.75742989805</v>
+        <v>13886.75742953947</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4336,19 +4336,19 @@
         <v>44166</v>
       </c>
       <c r="B29">
-        <v>13394.18377308944</v>
+        <v>13394.18377276959</v>
       </c>
       <c r="C29">
-        <v>14472.83427854741</v>
+        <v>14472.83427883219</v>
       </c>
       <c r="D29">
-        <v>12315.53326763147</v>
+        <v>12315.533266707</v>
       </c>
       <c r="E29">
-        <v>15551.48478400538</v>
+        <v>15551.48478489479</v>
       </c>
       <c r="F29">
-        <v>13933.50902581842</v>
+        <v>13933.50902580089</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4356,19 +4356,19 @@
         <v>44197</v>
       </c>
       <c r="B30">
-        <v>13481.20899339761</v>
+        <v>13481.20899303506</v>
       </c>
       <c r="C30">
-        <v>14543.8863755596</v>
+        <v>14543.88637582792</v>
       </c>
       <c r="D30">
-        <v>12418.53161123562</v>
+        <v>12418.5316102422</v>
       </c>
       <c r="E30">
-        <v>15606.5637577216</v>
+        <v>15606.56375862079</v>
       </c>
       <c r="F30">
-        <v>14012.54768447861</v>
+        <v>14012.54768443149</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4376,19 +4376,19 @@
         <v>44228</v>
       </c>
       <c r="B31">
-        <v>13665.76133906543</v>
+        <v>13665.76133870136</v>
       </c>
       <c r="C31">
-        <v>14723.78147067641</v>
+        <v>14723.78147102906</v>
       </c>
       <c r="D31">
-        <v>12607.74120745444</v>
+        <v>12607.74120637366</v>
       </c>
       <c r="E31">
-        <v>15781.80160228739</v>
+        <v>15781.80160335676</v>
       </c>
       <c r="F31">
-        <v>14194.77140487092</v>
+        <v>14194.77140486521</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4396,19 +4396,19 @@
         <v>44256</v>
       </c>
       <c r="B32">
-        <v>13474.00491827574</v>
+        <v>13474.00491799082</v>
       </c>
       <c r="C32">
-        <v>14505.22214432579</v>
+        <v>14505.22214463634</v>
       </c>
       <c r="D32">
-        <v>12442.78769222569</v>
+        <v>12442.7876913453</v>
       </c>
       <c r="E32">
-        <v>15536.43937037585</v>
+        <v>15536.43937128186</v>
       </c>
       <c r="F32">
-        <v>13989.61353130077</v>
+        <v>13989.61353131358</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4416,19 +4416,19 @@
         <v>44287</v>
       </c>
       <c r="B33">
-        <v>14201.02292533927</v>
+        <v>14201.02292484965</v>
       </c>
       <c r="C33">
-        <v>15282.97826480978</v>
+        <v>15282.97826525179</v>
       </c>
       <c r="D33">
-        <v>13119.06758586875</v>
+        <v>13119.06758444751</v>
       </c>
       <c r="E33">
-        <v>16364.9336042803</v>
+        <v>16364.93360565393</v>
       </c>
       <c r="F33">
-        <v>14742.00059507452</v>
+        <v>14742.00059505072</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4436,19 +4436,19 @@
         <v>44317</v>
       </c>
       <c r="B34">
-        <v>14036.87796103118</v>
+        <v>14036.87796061712</v>
       </c>
       <c r="C34">
-        <v>15108.76855531724</v>
+        <v>15108.76855580047</v>
       </c>
       <c r="D34">
-        <v>12964.98736674511</v>
+        <v>12964.98736543377</v>
       </c>
       <c r="E34">
-        <v>16180.6591496033</v>
+        <v>16180.65915098383</v>
       </c>
       <c r="F34">
-        <v>14572.8232581742</v>
+        <v>14572.8232582088</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4456,19 +4456,19 @@
         <v>44348</v>
       </c>
       <c r="B35">
-        <v>14148.65147514078</v>
+        <v>14148.65147474228</v>
       </c>
       <c r="C35">
-        <v>15201.07228929362</v>
+        <v>15201.07228981229</v>
       </c>
       <c r="D35">
-        <v>13096.23066098795</v>
+        <v>13096.23065967228</v>
       </c>
       <c r="E35">
-        <v>16253.49310344645</v>
+        <v>16253.4931048823</v>
       </c>
       <c r="F35">
-        <v>14674.8618822172</v>
+        <v>14674.86188227729</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4476,19 +4476,19 @@
         <v>44378</v>
       </c>
       <c r="B36">
-        <v>14291.11437991302</v>
+        <v>14291.11437948989</v>
       </c>
       <c r="C36">
-        <v>15336.99887151849</v>
+        <v>15336.99887205119</v>
       </c>
       <c r="D36">
-        <v>13245.22988830755</v>
+        <v>13245.22988692858</v>
       </c>
       <c r="E36">
-        <v>16382.88336312395</v>
+        <v>16382.8833646125</v>
       </c>
       <c r="F36">
-        <v>14814.05662571575</v>
+        <v>14814.05662577054</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4496,19 +4496,19 @@
         <v>44409</v>
       </c>
       <c r="B37">
-        <v>14248.10850505531</v>
+        <v>14248.10850466175</v>
       </c>
       <c r="C37">
-        <v>15276.54508690578</v>
+        <v>15276.54508742023</v>
       </c>
       <c r="D37">
-        <v>13219.67192320483</v>
+        <v>13219.67192190327</v>
       </c>
       <c r="E37">
-        <v>16304.98166875625</v>
+        <v>16304.98167017871</v>
       </c>
       <c r="F37">
-        <v>14762.32679598055</v>
+        <v>14762.32679604099</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4516,19 +4516,19 @@
         <v>44440</v>
       </c>
       <c r="B38">
-        <v>14412.04438276436</v>
+        <v>14412.04438230736</v>
       </c>
       <c r="C38">
-        <v>15431.29212372094</v>
+        <v>15431.29212418774</v>
       </c>
       <c r="D38">
-        <v>13392.79664180778</v>
+        <v>13392.79664042697</v>
       </c>
       <c r="E38">
-        <v>16450.53986467752</v>
+        <v>16450.53986606812</v>
       </c>
       <c r="F38">
-        <v>14921.66825324265</v>
+        <v>14921.66825324755</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4536,19 +4536,19 @@
         <v>44470</v>
       </c>
       <c r="B39">
-        <v>14420.47745789857</v>
+        <v>14420.47745745456</v>
       </c>
       <c r="C39">
-        <v>15428.16266080217</v>
+        <v>15428.16266124496</v>
       </c>
       <c r="D39">
-        <v>13412.79225499497</v>
+        <v>13412.79225366416</v>
       </c>
       <c r="E39">
-        <v>16435.84786370577</v>
+        <v>16435.84786503536</v>
       </c>
       <c r="F39">
-        <v>14924.32005935037</v>
+        <v>14924.32005934976</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4556,19 +4556,19 @@
         <v>44501</v>
       </c>
       <c r="B40">
-        <v>14539.38548522068</v>
+        <v>14539.38548477782</v>
       </c>
       <c r="C40">
-        <v>15539.9434140919</v>
+        <v>15539.9434145415</v>
       </c>
       <c r="D40">
-        <v>13538.82755634946</v>
+        <v>13538.82755501414</v>
       </c>
       <c r="E40">
-        <v>16540.50134296311</v>
+        <v>16540.50134430519</v>
       </c>
       <c r="F40">
-        <v>15039.66444965629</v>
+        <v>15039.66444965966</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4576,19 +4576,19 @@
         <v>44531</v>
       </c>
       <c r="B41">
-        <v>14543.8453903055</v>
+        <v>14543.84538988252</v>
       </c>
       <c r="C41">
-        <v>15532.80007555031</v>
+        <v>15532.80007598586</v>
       </c>
       <c r="D41">
-        <v>13554.89070506069</v>
+        <v>13554.89070377918</v>
       </c>
       <c r="E41">
-        <v>16521.75476079512</v>
+        <v>16521.7547620892</v>
       </c>
       <c r="F41">
-        <v>15038.3227329279</v>
+        <v>15038.32273293419</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4596,19 +4596,19 @@
         <v>44562</v>
       </c>
       <c r="B42">
-        <v>14516.71056840198</v>
+        <v>14516.71056799226</v>
       </c>
       <c r="C42">
-        <v>15490.34013243282</v>
+        <v>15490.34013282896</v>
       </c>
       <c r="D42">
-        <v>13543.08100437113</v>
+        <v>13543.08100315556</v>
       </c>
       <c r="E42">
-        <v>16463.96969646366</v>
+        <v>16463.96969766566</v>
       </c>
       <c r="F42">
-        <v>15003.5253504174</v>
+        <v>15003.52535041061</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4616,19 +4616,19 @@
         <v>44593</v>
       </c>
       <c r="B43">
-        <v>14546.42688613217</v>
+        <v>14546.42688574166</v>
       </c>
       <c r="C43">
-        <v>15508.10825180498</v>
+        <v>15508.10825218591</v>
       </c>
       <c r="D43">
-        <v>13584.74552045937</v>
+        <v>13584.74551929742</v>
       </c>
       <c r="E43">
-        <v>16469.78961747779</v>
+        <v>16469.78961863016</v>
       </c>
       <c r="F43">
-        <v>15027.26756896857</v>
+        <v>15027.26756896379</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4636,19 +4636,19 @@
         <v>44621</v>
       </c>
       <c r="B44">
-        <v>14548.73751515238</v>
+        <v>14548.73751478231</v>
       </c>
       <c r="C44">
-        <v>15499.569492549</v>
+        <v>15499.56949291377</v>
       </c>
       <c r="D44">
-        <v>13597.90553775576</v>
+        <v>13597.90553665085</v>
       </c>
       <c r="E44">
-        <v>16450.40146994562</v>
+        <v>16450.40147104523</v>
       </c>
       <c r="F44">
-        <v>15024.15350385069</v>
+        <v>15024.15350384804</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4656,19 +4656,19 @@
         <v>44652</v>
       </c>
       <c r="B45">
-        <v>14607.82685932516</v>
+        <v>14607.82685896444</v>
       </c>
       <c r="C45">
-        <v>15550.65060680182</v>
+        <v>15550.65060716181</v>
       </c>
       <c r="D45">
-        <v>13665.00311184851</v>
+        <v>13665.00311076706</v>
       </c>
       <c r="E45">
-        <v>16493.47435427847</v>
+        <v>16493.47435535919</v>
       </c>
       <c r="F45">
-        <v>15079.23873306349</v>
+        <v>15079.23873306312</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4676,19 +4676,19 @@
         <v>44682</v>
       </c>
       <c r="B46">
-        <v>14647.35664954203</v>
+        <v>14647.3566491837</v>
       </c>
       <c r="C46">
-        <v>15582.15861454089</v>
+        <v>15582.15861488734</v>
       </c>
       <c r="D46">
-        <v>13712.55468454316</v>
+        <v>13712.55468348005</v>
       </c>
       <c r="E46">
-        <v>16516.96057953975</v>
+        <v>16516.96058059099</v>
       </c>
       <c r="F46">
-        <v>15114.75763204146</v>
+        <v>15114.75763203552</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4696,19 +4696,19 @@
         <v>44713</v>
       </c>
       <c r="B47">
-        <v>14626.72851154295</v>
+        <v>14626.72851121154</v>
       </c>
       <c r="C47">
-        <v>15549.89194074856</v>
+        <v>15549.89194108652</v>
       </c>
       <c r="D47">
-        <v>13703.56508233735</v>
+        <v>13703.56508133657</v>
       </c>
       <c r="E47">
-        <v>16473.05536995416</v>
+        <v>16473.05537096149</v>
       </c>
       <c r="F47">
-        <v>15088.31022614576</v>
+        <v>15088.31022614903</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4716,19 +4716,19 @@
         <v>44743</v>
       </c>
       <c r="B48">
-        <v>14658.35564010594</v>
+        <v>14658.35563978694</v>
       </c>
       <c r="C48">
-        <v>15571.69511800092</v>
+        <v>15571.69511832855</v>
       </c>
       <c r="D48">
-        <v>13745.01616221095</v>
+        <v>13745.01616124533</v>
       </c>
       <c r="E48">
-        <v>16485.03459589592</v>
+        <v>16485.03459687017</v>
       </c>
       <c r="F48">
-        <v>15115.02537905343</v>
+        <v>15115.02537905775</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4736,19 +4736,19 @@
         <v>44774</v>
       </c>
       <c r="B49">
-        <v>14658.66410728393</v>
+        <v>14658.66410698007</v>
       </c>
       <c r="C49">
-        <v>15562.49397773811</v>
+        <v>15562.49397805269</v>
       </c>
       <c r="D49">
-        <v>13754.83423682975</v>
+        <v>13754.83423590744</v>
       </c>
       <c r="E49">
-        <v>16466.32384819228</v>
+        <v>16466.32384912532</v>
       </c>
       <c r="F49">
-        <v>15110.57904251102</v>
+        <v>15110.57904251638</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4756,19 +4756,19 @@
         <v>44805</v>
       </c>
       <c r="B50">
-        <v>14735.28655449467</v>
+        <v>14735.28655418417</v>
       </c>
       <c r="C50">
-        <v>15633.43744650023</v>
+        <v>15633.43744680347</v>
       </c>
       <c r="D50">
-        <v>13837.13566248911</v>
+        <v>13837.13566156488</v>
       </c>
       <c r="E50">
-        <v>16531.5883385058</v>
+        <v>16531.58833942276</v>
       </c>
       <c r="F50">
-        <v>15184.36200049745</v>
+        <v>15184.36200049382</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4776,19 +4776,19 @@
         <v>44835</v>
       </c>
       <c r="B51">
-        <v>14759.68428691699</v>
+        <v>14759.68428661271</v>
       </c>
       <c r="C51">
-        <v>15650.86381494405</v>
+        <v>15650.86381523915</v>
       </c>
       <c r="D51">
-        <v>13868.50475888992</v>
+        <v>13868.50475798626</v>
       </c>
       <c r="E51">
-        <v>16542.04334297112</v>
+        <v>16542.04334386559</v>
       </c>
       <c r="F51">
-        <v>15205.27405093052</v>
+        <v>15205.27405092593</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4796,19 +4796,19 @@
         <v>44866</v>
       </c>
       <c r="B52">
-        <v>14795.52084317089</v>
+        <v>14795.52084288186</v>
       </c>
       <c r="C52">
-        <v>15679.1139366137</v>
+        <v>15679.11393691112</v>
       </c>
       <c r="D52">
-        <v>13911.92774972808</v>
+        <v>13911.92774885259</v>
       </c>
       <c r="E52">
-        <v>16562.70703005651</v>
+        <v>16562.70703094038</v>
       </c>
       <c r="F52">
-        <v>15237.31738989229</v>
+        <v>15237.31738989649</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4816,19 +4816,19 @@
         <v>44896</v>
       </c>
       <c r="B53">
-        <v>14744.81882149407</v>
+        <v>14744.81882121532</v>
       </c>
       <c r="C53">
-        <v>15617.07992967472</v>
+        <v>15617.07992994618</v>
       </c>
       <c r="D53">
-        <v>13872.55771331341</v>
+        <v>13872.55771248445</v>
       </c>
       <c r="E53">
-        <v>16489.34103785538</v>
+        <v>16489.34103867705</v>
       </c>
       <c r="F53">
-        <v>15180.9493755844</v>
+        <v>15180.94937558075</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4836,19 +4836,19 @@
         <v>44927</v>
       </c>
       <c r="B54">
-        <v>14787.30922637073</v>
+        <v>14787.30922610133</v>
       </c>
       <c r="C54">
-        <v>15651.74324073058</v>
+        <v>15651.74324099577</v>
       </c>
       <c r="D54">
-        <v>13922.87521201088</v>
+        <v>13922.87521120688</v>
       </c>
       <c r="E54">
-        <v>16516.17725509044</v>
+        <v>16516.17725589022</v>
       </c>
       <c r="F54">
-        <v>15219.52623355066</v>
+        <v>15219.52623354855</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -4856,19 +4856,19 @@
         <v>44958</v>
       </c>
       <c r="B55">
-        <v>14943.56987316324</v>
+        <v>14943.56987281432</v>
       </c>
       <c r="C55">
-        <v>15808.69563983326</v>
+        <v>15808.69564003617</v>
       </c>
       <c r="D55">
-        <v>14078.44410649323</v>
+        <v>14078.44410559246</v>
       </c>
       <c r="E55">
-        <v>16673.82140650328</v>
+        <v>16673.82140725803</v>
       </c>
       <c r="F55">
-        <v>15376.13275649825</v>
+        <v>15376.13275642525</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4876,19 +4876,19 @@
         <v>44986</v>
       </c>
       <c r="B56">
-        <v>14906.31027643196</v>
+        <v>14906.31027614652</v>
       </c>
       <c r="C56">
-        <v>15763.93221511541</v>
+        <v>15763.93221535905</v>
       </c>
       <c r="D56">
-        <v>14048.6883377485</v>
+        <v>14048.68833693398</v>
       </c>
       <c r="E56">
-        <v>16621.55415379886</v>
+        <v>16621.55415457159</v>
       </c>
       <c r="F56">
-        <v>15335.12124577368</v>
+        <v>15335.12124575278</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4896,19 +4896,19 @@
         <v>45017</v>
       </c>
       <c r="B57">
-        <v>14913.18406532971</v>
+        <v>14913.18406506882</v>
       </c>
       <c r="C57">
-        <v>15761.33647530967</v>
+        <v>15761.33647555771</v>
       </c>
       <c r="D57">
-        <v>14065.03165534976</v>
+        <v>14065.03165457992</v>
       </c>
       <c r="E57">
-        <v>16609.48888528964</v>
+        <v>16609.48888604661</v>
       </c>
       <c r="F57">
-        <v>15337.2602703197</v>
+        <v>15337.26027031327</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4916,19 +4916,19 @@
         <v>45047</v>
       </c>
       <c r="B58">
-        <v>14945.22609469812</v>
+        <v>14945.22609445039</v>
       </c>
       <c r="C58">
-        <v>15786.89578212561</v>
+        <v>15786.89578237353</v>
       </c>
       <c r="D58">
-        <v>14103.55640727062</v>
+        <v>14103.55640652724</v>
       </c>
       <c r="E58">
-        <v>16628.5654695531</v>
+        <v>16628.56547029667</v>
       </c>
       <c r="F58">
-        <v>15366.06093841186</v>
+        <v>15366.06093841196</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4936,19 +4936,19 @@
         <v>45078</v>
       </c>
       <c r="B59">
-        <v>14964.25051811049</v>
+        <v>14964.2505178743</v>
       </c>
       <c r="C59">
-        <v>15799.5990791601</v>
+        <v>15799.59907940512</v>
       </c>
       <c r="D59">
-        <v>14128.90195706087</v>
+        <v>14128.90195634348</v>
       </c>
       <c r="E59">
-        <v>16634.94764020971</v>
+        <v>16634.94764093594</v>
       </c>
       <c r="F59">
-        <v>15381.92479863529</v>
+        <v>15381.92479863971</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4956,19 +4956,19 @@
         <v>45108</v>
       </c>
       <c r="B60">
-        <v>15008.86658293248</v>
+        <v>15008.86658269734</v>
       </c>
       <c r="C60">
-        <v>15838.98665747602</v>
+        <v>15838.98665771352</v>
       </c>
       <c r="D60">
-        <v>14178.74650838894</v>
+        <v>14178.74650768115</v>
       </c>
       <c r="E60">
-        <v>16669.10673201956</v>
+        <v>16669.10673272971</v>
       </c>
       <c r="F60">
-        <v>15423.92662020425</v>
+        <v>15423.92662020543</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4976,19 +4976,19 @@
         <v>45139</v>
       </c>
       <c r="B61">
-        <v>15074.25417749156</v>
+        <v>15074.25417725365</v>
       </c>
       <c r="C61">
-        <v>15901.04069373816</v>
+        <v>15901.04069397158</v>
       </c>
       <c r="D61">
-        <v>14247.46766124496</v>
+        <v>14247.46766053573</v>
       </c>
       <c r="E61">
-        <v>16727.82720998476</v>
+        <v>16727.8272106895</v>
       </c>
       <c r="F61">
-        <v>15487.64743561486</v>
+        <v>15487.64743561261</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -4996,19 +4996,19 @@
         <v>45170</v>
       </c>
       <c r="B62">
-        <v>15057.12412792205</v>
+        <v>15057.12412769818</v>
       </c>
       <c r="C62">
-        <v>15876.61892788149</v>
+        <v>15876.61892811135</v>
       </c>
       <c r="D62">
-        <v>14237.6293279626</v>
+        <v>14237.62932728502</v>
       </c>
       <c r="E62">
-        <v>16696.11372784094</v>
+        <v>16696.11372852451</v>
       </c>
       <c r="F62">
-        <v>15466.87152790177</v>
+        <v>15466.87152790476</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5016,16 +5016,16 @@
         <v>45200</v>
       </c>
       <c r="B63">
-        <v>15139.032508818</v>
+        <v>15139.03250859141</v>
       </c>
       <c r="C63">
-        <v>15954.63051241564</v>
+        <v>15954.63051264223</v>
       </c>
       <c r="D63">
-        <v>14323.43450522036</v>
+        <v>14323.4345045406</v>
       </c>
       <c r="E63">
-        <v>16770.22851601328</v>
+        <v>16770.22851669305</v>
       </c>
       <c r="F63">
         <v>15546.83151061682</v>
@@ -5036,19 +5036,19 @@
         <v>45231</v>
       </c>
       <c r="B64">
-        <v>15145.32306685473</v>
+        <v>15145.3230666262</v>
       </c>
       <c r="C64">
-        <v>15955.54617331631</v>
+        <v>15955.54617352924</v>
       </c>
       <c r="D64">
-        <v>14335.09996039316</v>
+        <v>14335.09995972317</v>
       </c>
       <c r="E64">
-        <v>16765.76927977788</v>
+        <v>16765.76928043227</v>
       </c>
       <c r="F64">
-        <v>15550.43462008552</v>
+        <v>15550.43462007772</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5056,19 +5056,19 @@
         <v>45261</v>
       </c>
       <c r="B65">
-        <v>15223.87754667119</v>
+        <v>15223.87754644817</v>
       </c>
       <c r="C65">
-        <v>16030.88257205007</v>
+        <v>16030.88257226923</v>
       </c>
       <c r="D65">
-        <v>14416.87252129231</v>
+        <v>14416.8725206271</v>
       </c>
       <c r="E65">
-        <v>16837.88759742895</v>
+        <v>16837.8875980903</v>
       </c>
       <c r="F65">
-        <v>15627.38005936063</v>
+        <v>15627.3800593587</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5076,16 +5076,16 @@
         <v>45292</v>
       </c>
       <c r="B66">
-        <v>15286.70561818967</v>
+        <v>15286.70561796862</v>
       </c>
       <c r="C66">
-        <v>16090.95586249821</v>
+        <v>16090.95586271925</v>
       </c>
       <c r="D66">
-        <v>14482.45537388113</v>
+        <v>14482.45537321798</v>
       </c>
       <c r="E66">
-        <v>16895.20610680674</v>
+        <v>16895.20610746989</v>
       </c>
       <c r="F66">
         <v>15688.83074034394</v>
@@ -5096,16 +5096,16 @@
         <v>45323</v>
       </c>
       <c r="B67">
-        <v>15223.22879801362</v>
+        <v>15223.22879780427</v>
       </c>
       <c r="C67">
-        <v>16018.83684519218</v>
+        <v>16018.83684540153</v>
       </c>
       <c r="D67">
-        <v>14427.62075083505</v>
+        <v>14427.620750207</v>
       </c>
       <c r="E67">
-        <v>16814.44489237075</v>
+        <v>16814.4448929988</v>
       </c>
       <c r="F67">
         <v>15621.0328216029</v>
@@ -5116,19 +5116,19 @@
         <v>45352</v>
       </c>
       <c r="B68">
-        <v>15304.41709002412</v>
+        <v>15304.41708980835</v>
       </c>
       <c r="C68">
-        <v>16095.75879664476</v>
+        <v>16095.75879684522</v>
       </c>
       <c r="D68">
-        <v>14513.07538340347</v>
+        <v>14513.07538277149</v>
       </c>
       <c r="E68">
-        <v>16887.10050326541</v>
+        <v>16887.10050388208</v>
       </c>
       <c r="F68">
-        <v>15700.08794333444</v>
+        <v>15700.08794332679</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5136,19 +5136,19 @@
         <v>45383</v>
       </c>
       <c r="B69">
-        <v>15334.11716112271</v>
+        <v>15334.11716092038</v>
       </c>
       <c r="C69">
-        <v>16122.04970052518</v>
+        <v>16122.0497007325</v>
       </c>
       <c r="D69">
-        <v>14546.18462172024</v>
+        <v>14546.18462110826</v>
       </c>
       <c r="E69">
-        <v>16909.98223992766</v>
+        <v>16909.98224054462</v>
       </c>
       <c r="F69">
-        <v>15728.08343082395</v>
+        <v>15728.08343082644</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -5156,16 +5156,16 @@
         <v>45413</v>
       </c>
       <c r="B70">
-        <v>15324.34818768421</v>
+        <v>15324.34818748579</v>
       </c>
       <c r="C70">
-        <v>16106.31828435949</v>
+        <v>16106.31828455791</v>
       </c>
       <c r="D70">
-        <v>14542.37809100892</v>
+        <v>14542.37809041366</v>
       </c>
       <c r="E70">
-        <v>16888.28838103477</v>
+        <v>16888.28838163003</v>
       </c>
       <c r="F70">
         <v>15715.33323602185</v>
@@ -5176,19 +5176,19 @@
         <v>45444</v>
       </c>
       <c r="B71">
-        <v>15431.64244942921</v>
+        <v>15431.64244922016</v>
       </c>
       <c r="C71">
-        <v>16212.02818489997</v>
+        <v>16212.02818509255</v>
       </c>
       <c r="D71">
-        <v>14651.25671395844</v>
+        <v>14651.25671334776</v>
       </c>
       <c r="E71">
-        <v>16992.41392037074</v>
+        <v>16992.41392096494</v>
       </c>
       <c r="F71">
-        <v>15821.83531716459</v>
+        <v>15821.83531715635</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5196,19 +5196,19 @@
         <v>45474</v>
       </c>
       <c r="B72">
-        <v>15447.6887111479</v>
+        <v>15447.6887109509</v>
       </c>
       <c r="C72">
-        <v>16224.4692011074</v>
+        <v>16224.46920130571</v>
       </c>
       <c r="D72">
-        <v>14670.9082211884</v>
+        <v>14670.90822059609</v>
       </c>
       <c r="E72">
-        <v>17001.2496910669</v>
+        <v>17001.24969166051</v>
       </c>
       <c r="F72">
-        <v>15836.07895612765</v>
+        <v>15836.0789561283</v>
       </c>
     </row>
   </sheetData>

--- a/app/analytical-backend/data/07_model_output/ar.xlsx
+++ b/app/analytical-backend/data/07_model_output/ar.xlsx
@@ -468,7 +468,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.9946202984165897</v>
+        <v>0.9946202985178637</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -476,7 +476,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002176552418256159</v>
+        <v>0.002176552408355443</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>152.2746023045191</v>
+        <v>152.274600871219</v>
       </c>
     </row>
   </sheetData>
@@ -2988,7 +2988,7 @@
         <v>43374</v>
       </c>
       <c r="B227">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="C227">
         <v>13727.1</v>
@@ -2999,7 +2999,7 @@
         <v>43405</v>
       </c>
       <c r="B228">
-        <v>13762.14655938816</v>
+        <v>13762.14655939053</v>
       </c>
       <c r="C228">
         <v>13800.3</v>
@@ -3010,7 +3010,7 @@
         <v>43435</v>
       </c>
       <c r="B229">
-        <v>13820.54392215984</v>
+        <v>13820.54392215916</v>
       </c>
       <c r="C229">
         <v>13682.3</v>
@@ -3021,7 +3021,7 @@
         <v>43466</v>
       </c>
       <c r="B230">
-        <v>13723.8440850211</v>
+        <v>13723.84408501996</v>
       </c>
       <c r="C230">
         <v>13716.5</v>
@@ -3032,7 +3032,7 @@
         <v>43497</v>
       </c>
       <c r="B231">
-        <v>13764.31487604686</v>
+        <v>13764.31487605139</v>
       </c>
       <c r="C231">
         <v>13723.1</v>
@@ -3043,7 +3043,7 @@
         <v>43525</v>
       </c>
       <c r="B232">
-        <v>13735.02464504945</v>
+        <v>13735.02464505133</v>
       </c>
       <c r="C232">
         <v>13818.2</v>
@@ -3054,7 +3054,7 @@
         <v>43556</v>
       </c>
       <c r="B233">
-        <v>13848.81486970803</v>
+        <v>13848.81486970863</v>
       </c>
       <c r="C233">
         <v>13813.1</v>
@@ -3076,7 +3076,7 @@
         <v>43617</v>
       </c>
       <c r="B235">
-        <v>13912.53444759663</v>
+        <v>13912.5344475934</v>
       </c>
       <c r="C235">
         <v>13909.09999999999</v>
@@ -3087,7 +3087,7 @@
         <v>43647</v>
       </c>
       <c r="B236">
-        <v>13935.17934710532</v>
+        <v>13935.17934710672</v>
       </c>
       <c r="C236">
         <v>13968.4</v>
@@ -3098,7 +3098,7 @@
         <v>43678</v>
       </c>
       <c r="B237">
-        <v>14003.01220215172</v>
+        <v>14003.01220207311</v>
       </c>
       <c r="C237">
         <v>14013.2</v>
@@ -3109,7 +3109,7 @@
         <v>43709</v>
       </c>
       <c r="B238">
-        <v>14046.40905810868</v>
+        <v>14046.40905817672</v>
       </c>
       <c r="C238">
         <v>14029.7</v>
@@ -3120,7 +3120,7 @@
         <v>43739</v>
       </c>
       <c r="B239">
-        <v>14068.36017746287</v>
+        <v>14068.36017744439</v>
       </c>
       <c r="C239">
         <v>14029.09999999999</v>
@@ -3131,7 +3131,7 @@
         <v>43770</v>
       </c>
       <c r="B240">
-        <v>14067.62969454793</v>
+        <v>14067.6296945775</v>
       </c>
       <c r="C240">
         <v>14115.39999999999</v>
@@ -3142,7 +3142,7 @@
         <v>43800</v>
       </c>
       <c r="B241">
-        <v>14144.31838326521</v>
+        <v>14144.3183830814</v>
       </c>
       <c r="C241">
         <v>14137.09999999999</v>
@@ -3153,7 +3153,7 @@
         <v>43831</v>
       </c>
       <c r="B242">
-        <v>14163.17337706021</v>
+        <v>14163.1733770597</v>
       </c>
       <c r="C242">
         <v>14184.79999999999</v>
@@ -3164,7 +3164,7 @@
         <v>43862</v>
       </c>
       <c r="B243">
-        <v>14227.57980055274</v>
+        <v>14227.57980265306</v>
       </c>
       <c r="C243">
         <v>14167.79999999999</v>
@@ -3175,7 +3175,7 @@
         <v>43891</v>
       </c>
       <c r="B244">
-        <v>14202.34670413345</v>
+        <v>14202.3467041327</v>
       </c>
       <c r="C244">
         <v>13234.29999999999</v>
@@ -3186,7 +3186,7 @@
         <v>43922</v>
       </c>
       <c r="B245">
-        <v>13298.35997385564</v>
+        <v>13298.35998117347</v>
       </c>
       <c r="C245">
         <v>11783.29999999999</v>
@@ -3197,7 +3197,7 @@
         <v>43952</v>
       </c>
       <c r="B246">
-        <v>11140.77789757389</v>
+        <v>11140.77794425926</v>
       </c>
       <c r="C246">
         <v>12757.99999999999</v>
@@ -3219,7 +3219,7 @@
         <v>44013</v>
       </c>
       <c r="B248">
-        <v>13170.83648895239</v>
+        <v>13170.83648895002</v>
       </c>
       <c r="C248">
         <v>13667.29999999999</v>
@@ -3230,7 +3230,7 @@
         <v>44044</v>
       </c>
       <c r="B249">
-        <v>13600.60622413137</v>
+        <v>13600.60622417108</v>
       </c>
       <c r="C249">
         <v>13761.09999999999</v>
@@ -3241,7 +3241,7 @@
         <v>44075</v>
       </c>
       <c r="B250">
-        <v>13675.15139630761</v>
+        <v>13675.15139658909</v>
       </c>
       <c r="C250">
         <v>13953.39999999999</v>
@@ -3252,7 +3252,7 @@
         <v>44105</v>
       </c>
       <c r="B251">
-        <v>13937.66236999403</v>
+        <v>13937.66236998339</v>
       </c>
       <c r="C251">
         <v>13988.6</v>
@@ -3263,7 +3263,7 @@
         <v>44136</v>
       </c>
       <c r="B252">
-        <v>13886.75742989805</v>
+        <v>13886.75742975664</v>
       </c>
       <c r="C252">
         <v>13953.9</v>
@@ -3274,7 +3274,7 @@
         <v>44166</v>
       </c>
       <c r="B253">
-        <v>13933.50902581842</v>
+        <v>13933.50902580089</v>
       </c>
       <c r="C253">
         <v>14006.3</v>
@@ -3285,7 +3285,7 @@
         <v>44197</v>
       </c>
       <c r="B254">
-        <v>14012.54768447861</v>
+        <v>14012.54768443149</v>
       </c>
       <c r="C254">
         <v>14180.7</v>
@@ -3296,7 +3296,7 @@
         <v>44228</v>
       </c>
       <c r="B255">
-        <v>14194.77140487092</v>
+        <v>14194.77140486521</v>
       </c>
       <c r="C255">
         <v>14037.8</v>
@@ -3307,7 +3307,7 @@
         <v>44256</v>
       </c>
       <c r="B256">
-        <v>13989.61353130077</v>
+        <v>13989.61353131358</v>
       </c>
       <c r="C256">
         <v>14629.3</v>
@@ -3318,7 +3318,7 @@
         <v>44287</v>
       </c>
       <c r="B257">
-        <v>14742.00059507452</v>
+        <v>14742.00059505072</v>
       </c>
       <c r="C257">
         <v>14730.7</v>
@@ -3329,7 +3329,7 @@
         <v>44317</v>
       </c>
       <c r="B258">
-        <v>14572.8232581742</v>
+        <v>14572.8232582088</v>
       </c>
       <c r="C258">
         <v>14689.59999999999</v>
@@ -3340,7 +3340,7 @@
         <v>44348</v>
       </c>
       <c r="B259">
-        <v>14674.8618822172</v>
+        <v>14674.86188227729</v>
       </c>
       <c r="C259">
         <v>14816.39999999999</v>
@@ -3351,7 +3351,7 @@
         <v>44378</v>
       </c>
       <c r="B260">
-        <v>14814.05662571575</v>
+        <v>14814.05662577054</v>
       </c>
       <c r="C260">
         <v>14784</v>
@@ -3362,7 +3362,7 @@
         <v>44409</v>
       </c>
       <c r="B261">
-        <v>14762.32679598055</v>
+        <v>14762.32679604099</v>
       </c>
       <c r="C261">
         <v>14863</v>
@@ -3373,7 +3373,7 @@
         <v>44440</v>
       </c>
       <c r="B262">
-        <v>14921.66825324265</v>
+        <v>14921.66825324755</v>
       </c>
       <c r="C262">
         <v>14899.4</v>
@@ -3384,7 +3384,7 @@
         <v>44470</v>
       </c>
       <c r="B263">
-        <v>14924.32005935037</v>
+        <v>14924.32005934976</v>
       </c>
       <c r="C263">
         <v>14997.3</v>
@@ -3395,7 +3395,7 @@
         <v>44501</v>
       </c>
       <c r="B264">
-        <v>15039.66444965629</v>
+        <v>15039.66444965966</v>
       </c>
       <c r="C264">
         <v>15019.2</v>
@@ -3406,7 +3406,7 @@
         <v>44531</v>
       </c>
       <c r="B265">
-        <v>15038.3227329279</v>
+        <v>15038.32273293419</v>
       </c>
       <c r="C265">
         <v>14970.4</v>
@@ -3417,7 +3417,7 @@
         <v>44562</v>
       </c>
       <c r="B266">
-        <v>15003.5253504174</v>
+        <v>15003.52535041061</v>
       </c>
       <c r="C266">
         <v>14971.1</v>
@@ -3428,7 +3428,7 @@
         <v>44593</v>
       </c>
       <c r="B267">
-        <v>15027.26756896857</v>
+        <v>15027.26756896379</v>
       </c>
       <c r="C267">
         <v>14980.6</v>
@@ -3439,7 +3439,7 @@
         <v>44621</v>
       </c>
       <c r="B268">
-        <v>15024.15350385069</v>
+        <v>15024.15350384804</v>
       </c>
       <c r="C268">
         <v>15034</v>
@@ -3450,7 +3450,7 @@
         <v>44652</v>
       </c>
       <c r="B269">
-        <v>15079.23873306349</v>
+        <v>15079.23873306528</v>
       </c>
       <c r="C269">
         <v>15081.7</v>
@@ -3461,7 +3461,7 @@
         <v>44682</v>
       </c>
       <c r="B270">
-        <v>15114.75763204146</v>
+        <v>15114.75763203552</v>
       </c>
       <c r="C270">
         <v>15060</v>
@@ -3472,7 +3472,7 @@
         <v>44713</v>
       </c>
       <c r="B271">
-        <v>15088.31022614576</v>
+        <v>15088.31022614903</v>
       </c>
       <c r="C271">
         <v>15065.8</v>
@@ -3483,7 +3483,7 @@
         <v>44743</v>
       </c>
       <c r="B272">
-        <v>15115.02537905343</v>
+        <v>15115.02537905775</v>
       </c>
       <c r="C272">
         <v>15069.1</v>
@@ -3494,7 +3494,7 @@
         <v>44774</v>
       </c>
       <c r="B273">
-        <v>15110.57904251102</v>
+        <v>15110.57904251638</v>
       </c>
       <c r="C273">
         <v>15136.3</v>
@@ -3505,7 +3505,7 @@
         <v>44805</v>
       </c>
       <c r="B274">
-        <v>15184.36200049745</v>
+        <v>15184.36200049382</v>
       </c>
       <c r="C274">
         <v>15176.7</v>
@@ -3516,7 +3516,7 @@
         <v>44835</v>
       </c>
       <c r="B275">
-        <v>15205.27405093052</v>
+        <v>15205.27405092593</v>
       </c>
       <c r="C275">
         <v>15202.7</v>
@@ -3527,7 +3527,7 @@
         <v>44866</v>
       </c>
       <c r="B276">
-        <v>15237.31738989229</v>
+        <v>15237.31738989649</v>
       </c>
       <c r="C276">
         <v>15149.8</v>
@@ -3538,7 +3538,7 @@
         <v>44896</v>
       </c>
       <c r="B277">
-        <v>15180.9493755844</v>
+        <v>15180.94937558075</v>
       </c>
       <c r="C277">
         <v>15161.7</v>
@@ -3549,7 +3549,7 @@
         <v>44927</v>
       </c>
       <c r="B278">
-        <v>15219.52623355066</v>
+        <v>15219.52623354855</v>
       </c>
       <c r="C278">
         <v>15317.6</v>
@@ -3560,7 +3560,7 @@
         <v>44958</v>
       </c>
       <c r="B279">
-        <v>15376.13275649825</v>
+        <v>15376.13275642525</v>
       </c>
       <c r="C279">
         <v>15325.5</v>
@@ -3571,7 +3571,7 @@
         <v>44986</v>
       </c>
       <c r="B280">
-        <v>15335.12124577368</v>
+        <v>15335.12124575278</v>
       </c>
       <c r="C280">
         <v>15295.4</v>
@@ -3582,7 +3582,7 @@
         <v>45017</v>
       </c>
       <c r="B281">
-        <v>15337.2602703197</v>
+        <v>15337.26027031327</v>
       </c>
       <c r="C281">
         <v>15316.9</v>
@@ -3593,7 +3593,7 @@
         <v>45047</v>
       </c>
       <c r="B282">
-        <v>15366.06093841186</v>
+        <v>15366.06093841196</v>
       </c>
       <c r="C282">
         <v>15337.4</v>
@@ -3604,7 +3604,7 @@
         <v>45078</v>
       </c>
       <c r="B283">
-        <v>15381.92479863529</v>
+        <v>15381.92479863971</v>
       </c>
       <c r="C283">
         <v>15376.3</v>
@@ -3615,7 +3615,7 @@
         <v>45108</v>
       </c>
       <c r="B284">
-        <v>15423.92662020425</v>
+        <v>15423.92662020543</v>
       </c>
       <c r="C284">
         <v>15448.3</v>
@@ -3626,7 +3626,7 @@
         <v>45139</v>
       </c>
       <c r="B285">
-        <v>15487.64743561486</v>
+        <v>15487.64743561261</v>
       </c>
       <c r="C285">
         <v>15439.79999999999</v>
@@ -3637,7 +3637,7 @@
         <v>45170</v>
       </c>
       <c r="B286">
-        <v>15466.87152790177</v>
+        <v>15466.87152790476</v>
       </c>
       <c r="C286">
         <v>15495.99999999999</v>
@@ -3659,7 +3659,7 @@
         <v>45231</v>
       </c>
       <c r="B288">
-        <v>15550.43462008552</v>
+        <v>15550.43462007772</v>
       </c>
       <c r="C288">
         <v>15584.29999999999</v>
@@ -3670,7 +3670,7 @@
         <v>45261</v>
       </c>
       <c r="B289">
-        <v>15627.38005936063</v>
+        <v>15627.3800593587</v>
       </c>
       <c r="C289">
         <v>15655.79999999999</v>
@@ -3703,7 +3703,7 @@
         <v>45352</v>
       </c>
       <c r="B292">
-        <v>15700.08794333444</v>
+        <v>15700.08794332679</v>
       </c>
       <c r="C292">
         <v>15689.59999999999</v>
@@ -3714,7 +3714,7 @@
         <v>45383</v>
       </c>
       <c r="B293">
-        <v>15728.08343082395</v>
+        <v>15728.08343082644</v>
       </c>
       <c r="C293">
         <v>15685.59999999999</v>
@@ -3736,7 +3736,7 @@
         <v>45444</v>
       </c>
       <c r="B295">
-        <v>15821.83531716459</v>
+        <v>15821.83531715635</v>
       </c>
       <c r="C295">
         <v>15810.7</v>
@@ -3747,7 +3747,7 @@
         <v>45474</v>
       </c>
       <c r="B296">
-        <v>15836.07895612765</v>
+        <v>15836.0789561283</v>
       </c>
       <c r="C296">
         <v>15870.29999999999</v>
@@ -3758,7 +3758,7 @@
         <v>45505</v>
       </c>
       <c r="B297">
-        <v>15911.45000807181</v>
+        <v>15911.45000806028</v>
       </c>
       <c r="C297">
         <v>16089.69999999999</v>
@@ -3816,19 +3816,19 @@
         <v>43374</v>
       </c>
       <c r="B3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="C3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="D3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="E3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
       <c r="F3">
-        <v>13722.78339408392</v>
+        <v>13722.78339408359</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3836,19 +3836,19 @@
         <v>43405</v>
       </c>
       <c r="B4">
-        <v>13720.13829566091</v>
+        <v>13720.13829566305</v>
       </c>
       <c r="C4">
-        <v>13804.15482311541</v>
+        <v>13804.15482311802</v>
       </c>
       <c r="D4">
-        <v>13636.1217682064</v>
+        <v>13636.12176820807</v>
       </c>
       <c r="E4">
-        <v>13888.17135056992</v>
+        <v>13888.171350573</v>
       </c>
       <c r="F4">
-        <v>13762.14655938816</v>
+        <v>13762.14655939053</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3856,19 +3856,19 @@
         <v>43435</v>
       </c>
       <c r="B5">
-        <v>13773.09436545825</v>
+        <v>13773.09436545861</v>
       </c>
       <c r="C5">
-        <v>13867.99347886143</v>
+        <v>13867.99347885971</v>
       </c>
       <c r="D5">
-        <v>13678.19525205506</v>
+        <v>13678.19525205751</v>
       </c>
       <c r="E5">
-        <v>13962.89259226462</v>
+        <v>13962.89259226081</v>
       </c>
       <c r="F5">
-        <v>13820.54392215984</v>
+        <v>13820.54392215916</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3876,19 +3876,19 @@
         <v>43466</v>
       </c>
       <c r="B6">
-        <v>13647.10123165385</v>
+        <v>13647.10123165372</v>
       </c>
       <c r="C6">
-        <v>13800.58693838835</v>
+        <v>13800.5869383862</v>
       </c>
       <c r="D6">
-        <v>13493.61552491934</v>
+        <v>13493.61552492123</v>
       </c>
       <c r="E6">
-        <v>13954.07264512285</v>
+        <v>13954.07264511869</v>
       </c>
       <c r="F6">
-        <v>13723.8440850211</v>
+        <v>13723.84408501996</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3896,19 +3896,19 @@
         <v>43497</v>
       </c>
       <c r="B7">
-        <v>13696.33813430579</v>
+        <v>13696.33813431104</v>
       </c>
       <c r="C7">
-        <v>13832.29161778794</v>
+        <v>13832.29161779174</v>
       </c>
       <c r="D7">
-        <v>13560.38465082363</v>
+        <v>13560.38465083034</v>
       </c>
       <c r="E7">
-        <v>13968.2451012701</v>
+        <v>13968.24510127245</v>
       </c>
       <c r="F7">
-        <v>13764.31487604686</v>
+        <v>13764.31487605139</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3916,19 +3916,19 @@
         <v>43525</v>
       </c>
       <c r="B8">
-        <v>13674.06508443986</v>
+        <v>13674.06508444226</v>
       </c>
       <c r="C8">
-        <v>13795.98420565905</v>
+        <v>13795.98420566039</v>
       </c>
       <c r="D8">
-        <v>13552.14596322067</v>
+        <v>13552.14596322413</v>
       </c>
       <c r="E8">
-        <v>13917.90332687824</v>
+        <v>13917.90332687852</v>
       </c>
       <c r="F8">
-        <v>13735.02464504945</v>
+        <v>13735.02464505133</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3936,19 +3936,19 @@
         <v>43556</v>
       </c>
       <c r="B9">
-        <v>13777.41152162746</v>
+        <v>13777.41152162869</v>
       </c>
       <c r="C9">
-        <v>13920.21821778861</v>
+        <v>13920.21821778857</v>
       </c>
       <c r="D9">
-        <v>13634.60482546631</v>
+        <v>13634.60482546882</v>
       </c>
       <c r="E9">
-        <v>14063.02491394976</v>
+        <v>14063.02491394844</v>
       </c>
       <c r="F9">
-        <v>13848.81486970803</v>
+        <v>13848.81486970863</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3956,16 +3956,16 @@
         <v>43586</v>
       </c>
       <c r="B10">
-        <v>13770.02614910731</v>
+        <v>13770.02614910791</v>
       </c>
       <c r="C10">
-        <v>13902.87858218283</v>
+        <v>13902.87858218223</v>
       </c>
       <c r="D10">
-        <v>13637.17371603179</v>
+        <v>13637.17371603358</v>
       </c>
       <c r="E10">
-        <v>14035.73101525835</v>
+        <v>14035.73101525655</v>
       </c>
       <c r="F10">
         <v>13836.45236564507</v>
@@ -3976,19 +3976,19 @@
         <v>43617</v>
       </c>
       <c r="B11">
-        <v>13848.0714537819</v>
+        <v>13848.07145377913</v>
       </c>
       <c r="C11">
-        <v>13976.99744141136</v>
+        <v>13976.99744140766</v>
       </c>
       <c r="D11">
-        <v>13719.14546615244</v>
+        <v>13719.14546615061</v>
       </c>
       <c r="E11">
-        <v>14105.92342904081</v>
+        <v>14105.92342903618</v>
       </c>
       <c r="F11">
-        <v>13912.53444759663</v>
+        <v>13912.5344475934</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3996,19 +3996,19 @@
         <v>43647</v>
       </c>
       <c r="B12">
-        <v>13874.12867182962</v>
+        <v>13874.12867183139</v>
       </c>
       <c r="C12">
-        <v>13996.23002238103</v>
+        <v>13996.23002238205</v>
       </c>
       <c r="D12">
-        <v>13752.02732127821</v>
+        <v>13752.02732128073</v>
       </c>
       <c r="E12">
-        <v>14118.33137293243</v>
+        <v>14118.33137293271</v>
       </c>
       <c r="F12">
-        <v>13935.17934710532</v>
+        <v>13935.17934710672</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4016,19 +4016,19 @@
         <v>43678</v>
       </c>
       <c r="B13">
-        <v>13943.21146214525</v>
+        <v>13943.21146206705</v>
       </c>
       <c r="C13">
-        <v>14062.81294215819</v>
+        <v>14062.81294207917</v>
       </c>
       <c r="D13">
-        <v>13823.6099821323</v>
+        <v>13823.60998205494</v>
       </c>
       <c r="E13">
-        <v>14182.41442217114</v>
+        <v>14182.41442209128</v>
       </c>
       <c r="F13">
-        <v>14003.01220215172</v>
+        <v>14003.01220207311</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4036,19 +4036,19 @@
         <v>43709</v>
       </c>
       <c r="B14">
-        <v>13988.95228625303</v>
+        <v>13988.9522863193</v>
       </c>
       <c r="C14">
-        <v>14103.86582996434</v>
+        <v>14103.86583003414</v>
       </c>
       <c r="D14">
-        <v>13874.03874254172</v>
+        <v>13874.03874260446</v>
       </c>
       <c r="E14">
-        <v>14218.77937367565</v>
+        <v>14218.77937374898</v>
       </c>
       <c r="F14">
-        <v>14046.40905810868</v>
+        <v>14046.40905817672</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4056,19 +4056,19 @@
         <v>43739</v>
       </c>
       <c r="B15">
-        <v>14013.21862204888</v>
+        <v>14013.2186220277</v>
       </c>
       <c r="C15">
-        <v>14123.50173287685</v>
+        <v>14123.50173286108</v>
       </c>
       <c r="D15">
-        <v>13902.9355112209</v>
+        <v>13902.93551119433</v>
       </c>
       <c r="E15">
-        <v>14233.78484370483</v>
+        <v>14233.78484369445</v>
       </c>
       <c r="F15">
-        <v>14068.36017746287</v>
+        <v>14068.36017744439</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4076,19 +4076,19 @@
         <v>43770</v>
       </c>
       <c r="B16">
-        <v>14013.98830969148</v>
+        <v>14013.98830971925</v>
       </c>
       <c r="C16">
-        <v>14121.27107940438</v>
+        <v>14121.27107943575</v>
       </c>
       <c r="D16">
-        <v>13906.70553997858</v>
+        <v>13906.70554000275</v>
       </c>
       <c r="E16">
-        <v>14228.55384911728</v>
+        <v>14228.55384915225</v>
       </c>
       <c r="F16">
-        <v>14067.62969454793</v>
+        <v>14067.6296945775</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4096,19 +4096,19 @@
         <v>43800</v>
       </c>
       <c r="B17">
-        <v>14090.18848166501</v>
+        <v>14090.18848148177</v>
       </c>
       <c r="C17">
-        <v>14198.44828486541</v>
+        <v>14198.44828468102</v>
       </c>
       <c r="D17">
-        <v>13981.9286784646</v>
+        <v>13981.92867828251</v>
       </c>
       <c r="E17">
-        <v>14306.70808806581</v>
+        <v>14306.70808788028</v>
       </c>
       <c r="F17">
-        <v>14144.31838326521</v>
+        <v>14144.3183830814</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4116,19 +4116,19 @@
         <v>43831</v>
       </c>
       <c r="B18">
-        <v>14110.79788747252</v>
+        <v>14110.7978874728</v>
       </c>
       <c r="C18">
-        <v>14215.54886664789</v>
+        <v>14215.5488666466</v>
       </c>
       <c r="D18">
-        <v>14006.04690829716</v>
+        <v>14006.04690829901</v>
       </c>
       <c r="E18">
-        <v>14320.29984582325</v>
+        <v>14320.29984582039</v>
       </c>
       <c r="F18">
-        <v>14163.17337706021</v>
+        <v>14163.1733770597</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4136,19 +4136,19 @@
         <v>43862</v>
       </c>
       <c r="B19">
-        <v>14176.24590498622</v>
+        <v>14176.24590708763</v>
       </c>
       <c r="C19">
-        <v>14278.91369611927</v>
+        <v>14278.91369821849</v>
       </c>
       <c r="D19">
-        <v>14073.57811385317</v>
+        <v>14073.57811595677</v>
       </c>
       <c r="E19">
-        <v>14381.58148725233</v>
+        <v>14381.58148934935</v>
       </c>
       <c r="F19">
-        <v>14227.57980055274</v>
+        <v>14227.57980265306</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4156,19 +4156,19 @@
         <v>43891</v>
       </c>
       <c r="B20">
-        <v>14150.93878897787</v>
+        <v>14150.93878885265</v>
       </c>
       <c r="C20">
-        <v>14253.75461928903</v>
+        <v>14253.75461941276</v>
       </c>
       <c r="D20">
-        <v>14048.1229586667</v>
+        <v>14048.12295829254</v>
       </c>
       <c r="E20">
-        <v>14356.57044960021</v>
+        <v>14356.57044997287</v>
       </c>
       <c r="F20">
-        <v>14202.34670413345</v>
+        <v>14202.3467041327</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4176,19 +4176,19 @@
         <v>43922</v>
       </c>
       <c r="B21">
-        <v>13087.33016305122</v>
+        <v>13087.33017036649</v>
       </c>
       <c r="C21">
-        <v>13509.38978466006</v>
+        <v>13509.38979198044</v>
       </c>
       <c r="D21">
-        <v>12665.27054144238</v>
+        <v>12665.27054875255</v>
       </c>
       <c r="E21">
-        <v>13931.4494062689</v>
+        <v>13931.44941359439</v>
       </c>
       <c r="F21">
-        <v>13298.35997385564</v>
+        <v>13298.35998117347</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4196,19 +4196,19 @@
         <v>43952</v>
       </c>
       <c r="B22">
-        <v>10797.24768653842</v>
+        <v>10797.2477320052</v>
       </c>
       <c r="C22">
-        <v>11484.30810860936</v>
+        <v>11484.30815651331</v>
       </c>
       <c r="D22">
-        <v>10110.18726446749</v>
+        <v>10110.18730749708</v>
       </c>
       <c r="E22">
-        <v>12171.36853068029</v>
+        <v>12171.36858102143</v>
       </c>
       <c r="F22">
-        <v>11140.77789757389</v>
+        <v>11140.77794425926</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4216,16 +4216,16 @@
         <v>43983</v>
       </c>
       <c r="B23">
-        <v>12794.01683542925</v>
+        <v>12794.01684275801</v>
       </c>
       <c r="C23">
-        <v>13886.95868693793</v>
+        <v>13886.95867960917</v>
       </c>
       <c r="D23">
-        <v>11701.07498392056</v>
+        <v>11701.07500590685</v>
       </c>
       <c r="E23">
-        <v>14979.90053844661</v>
+        <v>14979.90051646032</v>
       </c>
       <c r="F23">
         <v>13340.48776118359</v>
@@ -4236,19 +4236,19 @@
         <v>44013</v>
       </c>
       <c r="B24">
-        <v>12606.86969948374</v>
+        <v>12606.86970697469</v>
       </c>
       <c r="C24">
-        <v>13734.80327842104</v>
+        <v>13734.80327092535</v>
       </c>
       <c r="D24">
-        <v>11478.93612054644</v>
+        <v>11478.93614302402</v>
       </c>
       <c r="E24">
-        <v>14862.73685735835</v>
+        <v>14862.73683487602</v>
       </c>
       <c r="F24">
-        <v>13170.83648895239</v>
+        <v>13170.83648895002</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4256,19 +4256,19 @@
         <v>44044</v>
       </c>
       <c r="B25">
-        <v>13030.41443258497</v>
+        <v>13030.41443979635</v>
       </c>
       <c r="C25">
-        <v>14170.79801567777</v>
+        <v>14170.79800854581</v>
       </c>
       <c r="D25">
-        <v>11890.03084949216</v>
+        <v>11890.03087104689</v>
       </c>
       <c r="E25">
-        <v>15311.18159877057</v>
+        <v>15311.18157729526</v>
       </c>
       <c r="F25">
-        <v>13600.60622413137</v>
+        <v>13600.60622417108</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -4276,19 +4276,19 @@
         <v>44075</v>
       </c>
       <c r="B26">
-        <v>13112.63410669227</v>
+        <v>13112.6341139891</v>
       </c>
       <c r="C26">
-        <v>14237.66868592295</v>
+        <v>14237.66867918909</v>
       </c>
       <c r="D26">
-        <v>11987.59952746159</v>
+        <v>11987.5995487891</v>
       </c>
       <c r="E26">
-        <v>15362.70326515362</v>
+        <v>15362.70324438909</v>
       </c>
       <c r="F26">
-        <v>13675.15139630761</v>
+        <v>13675.15139658909</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4296,19 +4296,19 @@
         <v>44105</v>
       </c>
       <c r="B27">
-        <v>13376.48504803431</v>
+        <v>13376.48505490406</v>
       </c>
       <c r="C27">
-        <v>14498.83969195375</v>
+        <v>14498.83968506273</v>
       </c>
       <c r="D27">
-        <v>12254.13040411486</v>
+        <v>12254.1304247454</v>
       </c>
       <c r="E27">
-        <v>15621.1943358732</v>
+        <v>15621.19431522139</v>
       </c>
       <c r="F27">
-        <v>13937.66236999403</v>
+        <v>13937.66236998339</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4316,19 +4316,19 @@
         <v>44136</v>
       </c>
       <c r="B28">
-        <v>13335.48060047098</v>
+        <v>13335.48060708036</v>
       </c>
       <c r="C28">
-        <v>14438.03425932512</v>
+        <v>14438.03425243291</v>
       </c>
       <c r="D28">
-        <v>12232.92694161684</v>
+        <v>12232.92696172781</v>
       </c>
       <c r="E28">
-        <v>15540.58791817926</v>
+        <v>15540.58789778546</v>
       </c>
       <c r="F28">
-        <v>13886.75742989805</v>
+        <v>13886.75742975664</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4336,19 +4336,19 @@
         <v>44166</v>
       </c>
       <c r="B29">
-        <v>13394.18377308944</v>
+        <v>13394.18377966447</v>
       </c>
       <c r="C29">
-        <v>14472.83427854741</v>
+        <v>14472.83427193731</v>
       </c>
       <c r="D29">
-        <v>12315.53326763147</v>
+        <v>12315.53328739162</v>
       </c>
       <c r="E29">
-        <v>15551.48478400538</v>
+        <v>15551.48476421016</v>
       </c>
       <c r="F29">
-        <v>13933.50902581842</v>
+        <v>13933.50902580089</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4356,19 +4356,19 @@
         <v>44197</v>
       </c>
       <c r="B30">
-        <v>13481.20899339761</v>
+        <v>13481.20899983352</v>
       </c>
       <c r="C30">
-        <v>14543.8863755596</v>
+        <v>14543.88636902946</v>
       </c>
       <c r="D30">
-        <v>12418.53161123562</v>
+        <v>12418.53163063759</v>
       </c>
       <c r="E30">
-        <v>15606.5637577216</v>
+        <v>15606.5637382254</v>
       </c>
       <c r="F30">
-        <v>14012.54768447861</v>
+        <v>14012.54768443149</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4376,19 +4376,19 @@
         <v>44228</v>
       </c>
       <c r="B31">
-        <v>13665.76133906543</v>
+        <v>13665.76134547228</v>
       </c>
       <c r="C31">
-        <v>14723.78147067641</v>
+        <v>14723.78146425815</v>
       </c>
       <c r="D31">
-        <v>12607.74120745444</v>
+        <v>12607.74122668641</v>
       </c>
       <c r="E31">
-        <v>15781.80160228739</v>
+        <v>15781.80158304401</v>
       </c>
       <c r="F31">
-        <v>14194.77140487092</v>
+        <v>14194.77140486521</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -4396,19 +4396,19 @@
         <v>44256</v>
       </c>
       <c r="B32">
-        <v>13474.00491827574</v>
+        <v>13474.0049245397</v>
       </c>
       <c r="C32">
-        <v>14505.22214432579</v>
+        <v>14505.22213808746</v>
       </c>
       <c r="D32">
-        <v>12442.78769222569</v>
+        <v>12442.78771099195</v>
       </c>
       <c r="E32">
-        <v>15536.43937037585</v>
+        <v>15536.43935163521</v>
       </c>
       <c r="F32">
-        <v>13989.61353130077</v>
+        <v>13989.61353131358</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4416,19 +4416,19 @@
         <v>44287</v>
       </c>
       <c r="B33">
-        <v>14201.02292533927</v>
+        <v>14201.02293148318</v>
       </c>
       <c r="C33">
-        <v>15282.97826480978</v>
+        <v>15282.97825861826</v>
       </c>
       <c r="D33">
-        <v>13119.06758586875</v>
+        <v>13119.0676043481</v>
       </c>
       <c r="E33">
-        <v>16364.9336042803</v>
+        <v>16364.93358575334</v>
       </c>
       <c r="F33">
-        <v>14742.00059507452</v>
+        <v>14742.00059505072</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -4436,19 +4436,19 @@
         <v>44317</v>
       </c>
       <c r="B34">
-        <v>14036.87796103118</v>
+        <v>14036.87796718103</v>
       </c>
       <c r="C34">
-        <v>15108.76855531724</v>
+        <v>15108.76854923656</v>
       </c>
       <c r="D34">
-        <v>12964.98736674511</v>
+        <v>12964.98738512551</v>
       </c>
       <c r="E34">
-        <v>16180.6591496033</v>
+        <v>16180.65913129208</v>
       </c>
       <c r="F34">
-        <v>14572.8232581742</v>
+        <v>14572.8232582088</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -4456,19 +4456,19 @@
         <v>44348</v>
       </c>
       <c r="B35">
-        <v>14148.65147514078</v>
+        <v>14148.6514811915</v>
       </c>
       <c r="C35">
-        <v>15201.07228929362</v>
+        <v>15201.07228336307</v>
       </c>
       <c r="D35">
-        <v>13096.23066098795</v>
+        <v>13096.23067901993</v>
       </c>
       <c r="E35">
-        <v>16253.49310344645</v>
+        <v>16253.49308553464</v>
       </c>
       <c r="F35">
-        <v>14674.8618822172</v>
+        <v>14674.86188227729</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -4476,19 +4476,19 @@
         <v>44378</v>
       </c>
       <c r="B36">
-        <v>14291.11437991302</v>
+        <v>14291.11438590289</v>
       </c>
       <c r="C36">
-        <v>15336.99887151849</v>
+        <v>15336.99886563818</v>
       </c>
       <c r="D36">
-        <v>13245.22988830755</v>
+        <v>13245.2299061676</v>
       </c>
       <c r="E36">
-        <v>16382.88336312395</v>
+        <v>16382.88334537348</v>
       </c>
       <c r="F36">
-        <v>14814.05662571575</v>
+        <v>14814.05662577054</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -4496,19 +4496,19 @@
         <v>44409</v>
       </c>
       <c r="B37">
-        <v>14248.10850505531</v>
+        <v>14248.10851095649</v>
       </c>
       <c r="C37">
-        <v>15276.54508690578</v>
+        <v>15276.5450811255</v>
       </c>
       <c r="D37">
-        <v>13219.67192320483</v>
+        <v>13219.67194078747</v>
       </c>
       <c r="E37">
-        <v>16304.98166875625</v>
+        <v>16304.98165129452</v>
       </c>
       <c r="F37">
-        <v>14762.32679598055</v>
+        <v>14762.32679604099</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -4516,19 +4516,19 @@
         <v>44440</v>
       </c>
       <c r="B38">
-        <v>14412.04438276436</v>
+        <v>14412.04438854938</v>
       </c>
       <c r="C38">
-        <v>15431.29212372094</v>
+        <v>15431.29211794572</v>
       </c>
       <c r="D38">
-        <v>13392.79664180778</v>
+        <v>13392.79665915303</v>
       </c>
       <c r="E38">
-        <v>16450.53986467752</v>
+        <v>16450.53984734206</v>
       </c>
       <c r="F38">
-        <v>14921.66825324265</v>
+        <v>14921.66825324755</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -4536,19 +4536,19 @@
         <v>44470</v>
       </c>
       <c r="B39">
-        <v>14420.47745789857</v>
+        <v>14420.47746361668</v>
       </c>
       <c r="C39">
-        <v>15428.16266080217</v>
+        <v>15428.16265508284</v>
       </c>
       <c r="D39">
-        <v>13412.79225499497</v>
+        <v>13412.79227215052</v>
       </c>
       <c r="E39">
-        <v>16435.84786370577</v>
+        <v>16435.847846549</v>
       </c>
       <c r="F39">
-        <v>14924.32005935037</v>
+        <v>14924.32005934976</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -4556,19 +4556,19 @@
         <v>44501</v>
       </c>
       <c r="B40">
-        <v>14539.38548522068</v>
+        <v>14539.38549089859</v>
       </c>
       <c r="C40">
-        <v>15539.9434140919</v>
+        <v>15539.94340842073</v>
       </c>
       <c r="D40">
-        <v>13538.82755634946</v>
+        <v>13538.82757337645</v>
       </c>
       <c r="E40">
-        <v>16540.50134296311</v>
+        <v>16540.50132594287</v>
       </c>
       <c r="F40">
-        <v>15039.66444965629</v>
+        <v>15039.66444965966</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -4576,19 +4576,19 @@
         <v>44531</v>
       </c>
       <c r="B41">
-        <v>14543.8453903055</v>
+        <v>14543.84539592421</v>
       </c>
       <c r="C41">
-        <v>15532.80007555031</v>
+        <v>15532.80006994417</v>
       </c>
       <c r="D41">
-        <v>13554.89070506069</v>
+        <v>13554.89072190426</v>
       </c>
       <c r="E41">
-        <v>16521.75476079512</v>
+        <v>16521.75474396413</v>
       </c>
       <c r="F41">
-        <v>15038.3227329279</v>
+        <v>15038.32273293419</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -4596,19 +4596,19 @@
         <v>44562</v>
       </c>
       <c r="B42">
-        <v>14516.71056840198</v>
+        <v>14516.71057392373</v>
       </c>
       <c r="C42">
-        <v>15490.34013243282</v>
+        <v>15490.34012689749</v>
       </c>
       <c r="D42">
-        <v>13543.08100437113</v>
+        <v>13543.08102094997</v>
       </c>
       <c r="E42">
-        <v>16463.96969646366</v>
+        <v>16463.96967987126</v>
       </c>
       <c r="F42">
-        <v>15003.5253504174</v>
+        <v>15003.52535041061</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -4616,19 +4616,19 @@
         <v>44593</v>
       </c>
       <c r="B43">
-        <v>14546.42688613217</v>
+        <v>14546.4268915915</v>
       </c>
       <c r="C43">
-        <v>15508.10825180498</v>
+        <v>15508.10824633608</v>
       </c>
       <c r="D43">
-        <v>13584.74552045937</v>
+        <v>13584.74553684691</v>
       </c>
       <c r="E43">
-        <v>16469.78961747779</v>
+        <v>16469.78960108066</v>
       </c>
       <c r="F43">
-        <v>15027.26756896857</v>
+        <v>15027.26756896379</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -4636,19 +4636,19 @@
         <v>44621</v>
       </c>
       <c r="B44">
-        <v>14548.73751515238</v>
+        <v>14548.73752055539</v>
       </c>
       <c r="C44">
-        <v>15499.569492549</v>
+        <v>15499.5694871407</v>
       </c>
       <c r="D44">
-        <v>13597.90553775576</v>
+        <v>13597.90555397008</v>
       </c>
       <c r="E44">
-        <v>16450.40146994562</v>
+        <v>16450.401453726</v>
       </c>
       <c r="F44">
-        <v>15024.15350385069</v>
+        <v>15024.15350384804</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -4656,19 +4656,19 @@
         <v>44652</v>
       </c>
       <c r="B45">
-        <v>14607.82685932516</v>
+        <v>14607.8268646888</v>
       </c>
       <c r="C45">
-        <v>15550.65060680182</v>
+        <v>15550.65060144177</v>
       </c>
       <c r="D45">
-        <v>13665.00311184851</v>
+        <v>13665.00312793582</v>
       </c>
       <c r="E45">
-        <v>16493.47435427847</v>
+        <v>16493.47433819475</v>
       </c>
       <c r="F45">
-        <v>15079.23873306349</v>
+        <v>15079.23873306528</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -4676,19 +4676,19 @@
         <v>44682</v>
       </c>
       <c r="B46">
-        <v>14647.35664954203</v>
+        <v>14647.35665485428</v>
       </c>
       <c r="C46">
-        <v>15582.15861454089</v>
+        <v>15582.15860921675</v>
       </c>
       <c r="D46">
-        <v>13712.55468454316</v>
+        <v>13712.55470049181</v>
       </c>
       <c r="E46">
-        <v>16516.96057953975</v>
+        <v>16516.96056357923</v>
       </c>
       <c r="F46">
-        <v>15114.75763204146</v>
+        <v>15114.75763203552</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -4696,19 +4696,19 @@
         <v>44713</v>
       </c>
       <c r="B47">
-        <v>14626.72851154295</v>
+        <v>14626.72851680076</v>
       </c>
       <c r="C47">
-        <v>15549.89194074856</v>
+        <v>15549.8919354973</v>
       </c>
       <c r="D47">
-        <v>13703.56508233735</v>
+        <v>13703.56509810423</v>
       </c>
       <c r="E47">
-        <v>16473.05536995416</v>
+        <v>16473.05535419384</v>
       </c>
       <c r="F47">
-        <v>15088.31022614576</v>
+        <v>15088.31022614903</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -4716,19 +4716,19 @@
         <v>44743</v>
       </c>
       <c r="B48">
-        <v>14658.35564010594</v>
+        <v>14658.3556453113</v>
       </c>
       <c r="C48">
-        <v>15571.69511800092</v>
+        <v>15571.69511280419</v>
       </c>
       <c r="D48">
-        <v>13745.01616221095</v>
+        <v>13745.01617781841</v>
       </c>
       <c r="E48">
-        <v>16485.03459589592</v>
+        <v>16485.03458029708</v>
       </c>
       <c r="F48">
-        <v>15115.02537905343</v>
+        <v>15115.02537905775</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -4736,19 +4736,19 @@
         <v>44774</v>
       </c>
       <c r="B49">
-        <v>14658.66410728393</v>
+        <v>14658.66411243855</v>
       </c>
       <c r="C49">
-        <v>15562.49397773811</v>
+        <v>15562.49397259421</v>
       </c>
       <c r="D49">
-        <v>13754.83423682975</v>
+        <v>13754.83425228288</v>
       </c>
       <c r="E49">
-        <v>16466.32384819228</v>
+        <v>16466.32383274988</v>
       </c>
       <c r="F49">
-        <v>15110.57904251102</v>
+        <v>15110.57904251638</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -4756,19 +4756,19 @@
         <v>44805</v>
       </c>
       <c r="B50">
-        <v>14735.28655449467</v>
+        <v>14735.28655960815</v>
       </c>
       <c r="C50">
-        <v>15633.43744650023</v>
+        <v>15633.43744137949</v>
       </c>
       <c r="D50">
-        <v>13837.13566248911</v>
+        <v>13837.13567783681</v>
       </c>
       <c r="E50">
-        <v>16531.5883385058</v>
+        <v>16531.58832315083</v>
       </c>
       <c r="F50">
-        <v>15184.36200049745</v>
+        <v>15184.36200049382</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -4776,19 +4776,19 @@
         <v>44835</v>
       </c>
       <c r="B51">
-        <v>14759.68428691699</v>
+        <v>14759.68429199157</v>
       </c>
       <c r="C51">
-        <v>15650.86381494405</v>
+        <v>15650.86380986028</v>
       </c>
       <c r="D51">
-        <v>13868.50475888992</v>
+        <v>13868.50477412287</v>
       </c>
       <c r="E51">
-        <v>16542.04334297112</v>
+        <v>16542.04332772899</v>
       </c>
       <c r="F51">
-        <v>15205.27405093052</v>
+        <v>15205.27405092593</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -4796,19 +4796,19 @@
         <v>44866</v>
       </c>
       <c r="B52">
-        <v>14795.52084317089</v>
+        <v>14795.52084821256</v>
       </c>
       <c r="C52">
-        <v>15679.1139366137</v>
+        <v>15679.11393158041</v>
       </c>
       <c r="D52">
-        <v>13911.92774972808</v>
+        <v>13911.92776484471</v>
       </c>
       <c r="E52">
-        <v>16562.70703005651</v>
+        <v>16562.70701494826</v>
       </c>
       <c r="F52">
-        <v>15237.31738989229</v>
+        <v>15237.31738989649</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -4816,19 +4816,19 @@
         <v>44896</v>
       </c>
       <c r="B53">
-        <v>14744.81882149407</v>
+        <v>14744.81882646383</v>
       </c>
       <c r="C53">
-        <v>15617.07992967472</v>
+        <v>15617.07992469768</v>
       </c>
       <c r="D53">
-        <v>13872.55771331341</v>
+        <v>13872.55772822998</v>
       </c>
       <c r="E53">
-        <v>16489.34103785538</v>
+        <v>16489.34102293152</v>
       </c>
       <c r="F53">
-        <v>15180.9493755844</v>
+        <v>15180.94937558075</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -4836,19 +4836,19 @@
         <v>44927</v>
       </c>
       <c r="B54">
-        <v>14787.30922637073</v>
+        <v>14787.30923129915</v>
       </c>
       <c r="C54">
-        <v>15651.74324073058</v>
+        <v>15651.74323579795</v>
       </c>
       <c r="D54">
-        <v>13922.87521201088</v>
+        <v>13922.87522680036</v>
       </c>
       <c r="E54">
-        <v>16516.17725509044</v>
+        <v>16516.17724029674</v>
       </c>
       <c r="F54">
-        <v>15219.52623355066</v>
+        <v>15219.52623354855</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -4856,19 +4856,19 @@
         <v>44958</v>
       </c>
       <c r="B55">
-        <v>14943.56987316324</v>
+        <v>14943.56987801749</v>
       </c>
       <c r="C55">
-        <v>15808.69563983326</v>
+        <v>15808.695634833</v>
       </c>
       <c r="D55">
-        <v>14078.44410649323</v>
+        <v>14078.44412120198</v>
       </c>
       <c r="E55">
-        <v>16673.82140650328</v>
+        <v>16673.82139164852</v>
       </c>
       <c r="F55">
-        <v>15376.13275649825</v>
+        <v>15376.13275642525</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -4876,19 +4876,19 @@
         <v>44986</v>
       </c>
       <c r="B56">
-        <v>14906.31027643196</v>
+        <v>14906.3102812974</v>
       </c>
       <c r="C56">
-        <v>15763.93221511541</v>
+        <v>15763.93221020817</v>
       </c>
       <c r="D56">
-        <v>14048.6883377485</v>
+        <v>14048.68835238661</v>
       </c>
       <c r="E56">
-        <v>16621.55415379886</v>
+        <v>16621.55413911895</v>
       </c>
       <c r="F56">
-        <v>15335.12124577368</v>
+        <v>15335.12124575278</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -4896,19 +4896,19 @@
         <v>45017</v>
       </c>
       <c r="B57">
-        <v>14913.18406532971</v>
+        <v>14913.18407015735</v>
       </c>
       <c r="C57">
-        <v>15761.33647530967</v>
+        <v>15761.33647046918</v>
       </c>
       <c r="D57">
-        <v>14065.03165534976</v>
+        <v>14065.03166984552</v>
       </c>
       <c r="E57">
-        <v>16609.48888528964</v>
+        <v>16609.48887078101</v>
       </c>
       <c r="F57">
-        <v>15337.2602703197</v>
+        <v>15337.26027031327</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -4916,19 +4916,19 @@
         <v>45047</v>
       </c>
       <c r="B58">
-        <v>14945.22609469812</v>
+        <v>14945.22609949683</v>
       </c>
       <c r="C58">
-        <v>15786.89578212561</v>
+        <v>15786.89577732709</v>
       </c>
       <c r="D58">
-        <v>14103.55640727062</v>
+        <v>14103.55642166656</v>
       </c>
       <c r="E58">
-        <v>16628.5654695531</v>
+        <v>16628.56545515736</v>
       </c>
       <c r="F58">
-        <v>15366.06093841186</v>
+        <v>15366.06093841196</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4936,19 +4936,19 @@
         <v>45078</v>
       </c>
       <c r="B59">
-        <v>14964.25051811049</v>
+        <v>14964.25052287897</v>
       </c>
       <c r="C59">
-        <v>15799.5990791601</v>
+        <v>15799.59907440045</v>
       </c>
       <c r="D59">
-        <v>14128.90195706087</v>
+        <v>14128.9019713575</v>
       </c>
       <c r="E59">
-        <v>16634.94764020971</v>
+        <v>16634.94762592192</v>
       </c>
       <c r="F59">
-        <v>15381.92479863529</v>
+        <v>15381.92479863971</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -4956,19 +4956,19 @@
         <v>45108</v>
       </c>
       <c r="B60">
-        <v>15008.86658293248</v>
+        <v>15008.86658766899</v>
       </c>
       <c r="C60">
-        <v>15838.98665747602</v>
+        <v>15838.98665274187</v>
       </c>
       <c r="D60">
-        <v>14178.74650838894</v>
+        <v>14178.7465225961</v>
       </c>
       <c r="E60">
-        <v>16669.10673201956</v>
+        <v>16669.10671781476</v>
       </c>
       <c r="F60">
-        <v>15423.92662020425</v>
+        <v>15423.92662020543</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -4976,19 +4976,19 @@
         <v>45139</v>
       </c>
       <c r="B61">
-        <v>15074.25417749156</v>
+        <v>15074.25418220547</v>
       </c>
       <c r="C61">
-        <v>15901.04069373816</v>
+        <v>15901.04068901976</v>
       </c>
       <c r="D61">
-        <v>14247.46766124496</v>
+        <v>14247.46767539118</v>
       </c>
       <c r="E61">
-        <v>16727.82720998476</v>
+        <v>16727.82719583404</v>
       </c>
       <c r="F61">
-        <v>15487.64743561486</v>
+        <v>15487.64743561261</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -4996,19 +4996,19 @@
         <v>45170</v>
       </c>
       <c r="B62">
-        <v>15057.12412792205</v>
+        <v>15057.12413260082</v>
       </c>
       <c r="C62">
-        <v>15876.61892788149</v>
+        <v>15876.61892320871</v>
       </c>
       <c r="D62">
-        <v>14237.6293279626</v>
+        <v>14237.62934199293</v>
       </c>
       <c r="E62">
-        <v>16696.11372784094</v>
+        <v>16696.11371381659</v>
       </c>
       <c r="F62">
-        <v>15466.87152790177</v>
+        <v>15466.87152790476</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -5016,16 +5016,16 @@
         <v>45200</v>
       </c>
       <c r="B63">
-        <v>15139.032508818</v>
+        <v>15139.03251347109</v>
       </c>
       <c r="C63">
-        <v>15954.63051241564</v>
+        <v>15954.63050776255</v>
       </c>
       <c r="D63">
-        <v>14323.43450522036</v>
+        <v>14323.43451917963</v>
       </c>
       <c r="E63">
-        <v>16770.22851601328</v>
+        <v>16770.22850205401</v>
       </c>
       <c r="F63">
         <v>15546.83151061682</v>
@@ -5036,19 +5036,19 @@
         <v>45231</v>
       </c>
       <c r="B64">
-        <v>15145.32306685473</v>
+        <v>15145.32307147058</v>
       </c>
       <c r="C64">
-        <v>15955.54617331631</v>
+        <v>15955.54616868486</v>
       </c>
       <c r="D64">
-        <v>14335.09996039316</v>
+        <v>14335.09997425629</v>
       </c>
       <c r="E64">
-        <v>16765.76927977788</v>
+        <v>16765.76926589914</v>
       </c>
       <c r="F64">
-        <v>15550.43462008552</v>
+        <v>15550.43462007772</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -5056,19 +5056,19 @@
         <v>45261</v>
       </c>
       <c r="B65">
-        <v>15223.87754667119</v>
+        <v>15223.8775512738</v>
       </c>
       <c r="C65">
-        <v>16030.88257205007</v>
+        <v>16030.8825674436</v>
       </c>
       <c r="D65">
-        <v>14416.87252129231</v>
+        <v>14416.872535104</v>
       </c>
       <c r="E65">
-        <v>16837.88759742895</v>
+        <v>16837.8875836134</v>
       </c>
       <c r="F65">
-        <v>15627.38005936063</v>
+        <v>15627.3800593587</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -5076,16 +5076,16 @@
         <v>45292</v>
       </c>
       <c r="B66">
-        <v>15286.70561818967</v>
+        <v>15286.70562277809</v>
       </c>
       <c r="C66">
-        <v>16090.95586249821</v>
+        <v>16090.95585790978</v>
       </c>
       <c r="D66">
-        <v>14482.45537388113</v>
+        <v>14482.45538764639</v>
       </c>
       <c r="E66">
-        <v>16895.20610680674</v>
+        <v>16895.20609304148</v>
       </c>
       <c r="F66">
         <v>15688.83074034394</v>
@@ -5096,16 +5096,16 @@
         <v>45323</v>
       </c>
       <c r="B67">
-        <v>15223.22879801362</v>
+        <v>15223.22880255235</v>
       </c>
       <c r="C67">
-        <v>16018.83684519218</v>
+        <v>16018.83684065345</v>
       </c>
       <c r="D67">
-        <v>14427.62075083505</v>
+        <v>14427.62076445125</v>
       </c>
       <c r="E67">
-        <v>16814.44489237075</v>
+        <v>16814.44487875455</v>
       </c>
       <c r="F67">
         <v>15621.0328216029</v>
@@ -5116,19 +5116,19 @@
         <v>45352</v>
       </c>
       <c r="B68">
-        <v>15304.41709002412</v>
+        <v>15304.41709453092</v>
       </c>
       <c r="C68">
-        <v>16095.75879664476</v>
+        <v>16095.75879212265</v>
       </c>
       <c r="D68">
-        <v>14513.07538340347</v>
+        <v>14513.07539693918</v>
       </c>
       <c r="E68">
-        <v>16887.10050326541</v>
+        <v>16887.10048971439</v>
       </c>
       <c r="F68">
-        <v>15700.08794333444</v>
+        <v>15700.08794332679</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -5136,19 +5136,19 @@
         <v>45383</v>
       </c>
       <c r="B69">
-        <v>15334.11716112271</v>
+        <v>15334.11716562108</v>
       </c>
       <c r="C69">
-        <v>16122.04970052518</v>
+        <v>16122.0496960318</v>
       </c>
       <c r="D69">
-        <v>14546.18462172024</v>
+        <v>14546.18463521036</v>
       </c>
       <c r="E69">
-        <v>16909.98223992766</v>
+        <v>16909.98222644252</v>
       </c>
       <c r="F69">
-        <v>15728.08343082395</v>
+        <v>15728.08343082644</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -5156,16 +5156,16 @@
         <v>45413</v>
       </c>
       <c r="B70">
-        <v>15324.34818768421</v>
+        <v>15324.34819214697</v>
       </c>
       <c r="C70">
-        <v>16106.31828435949</v>
+        <v>16106.31827989673</v>
       </c>
       <c r="D70">
-        <v>14542.37809100892</v>
+        <v>14542.3781043972</v>
       </c>
       <c r="E70">
-        <v>16888.28838103477</v>
+        <v>16888.2883676465</v>
       </c>
       <c r="F70">
         <v>15715.33323602185</v>
@@ -5176,19 +5176,19 @@
         <v>45444</v>
       </c>
       <c r="B71">
-        <v>15431.64244942921</v>
+        <v>15431.64245387265</v>
       </c>
       <c r="C71">
-        <v>16212.02818489997</v>
+        <v>16212.02818044006</v>
       </c>
       <c r="D71">
-        <v>14651.25671395844</v>
+        <v>14651.25672730524</v>
       </c>
       <c r="E71">
-        <v>16992.41392037074</v>
+        <v>16992.41390700747</v>
       </c>
       <c r="F71">
-        <v>15821.83531716459</v>
+        <v>15821.83531715635</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -5196,19 +5196,19 @@
         <v>45474</v>
       </c>
       <c r="B72">
-        <v>15447.6887111479</v>
+        <v>15447.68871558047</v>
       </c>
       <c r="C72">
-        <v>16224.4692011074</v>
+        <v>16224.46919667614</v>
       </c>
       <c r="D72">
-        <v>14670.9082211884</v>
+        <v>14670.90823448479</v>
       </c>
       <c r="E72">
-        <v>17001.2496910669</v>
+        <v>17001.24967777182</v>
       </c>
       <c r="F72">
-        <v>15836.07895612765</v>
+        <v>15836.0789561283</v>
       </c>
     </row>
   </sheetData>
